--- a/commission/karin/2026-08.xlsx
+++ b/commission/karin/2026-08.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="57">
   <si>
     <t>Equine Performance Labs, LLC</t>
   </si>
@@ -37,6 +37,12 @@
     <t>Q3 Route C Accelerator — tiered on invoiced revenue when $30K gate met (else standard waterfall)</t>
   </si>
   <si>
+    <t>Basis</t>
+  </si>
+  <si>
+    <t>✅ CRM + QuickBooks reconciled (paid on cleared)</t>
+  </si>
+  <si>
     <t>Route C — Q3 Accelerator</t>
   </si>
   <si>
@@ -49,19 +55,19 @@
     <t>New / Reactivated (15%)</t>
   </si>
   <si>
-    <t>on $21,900.00 collected</t>
+    <t>on $17,100.00 collected</t>
   </si>
   <si>
     <t>Growth above baseline (12.5%)</t>
   </si>
   <si>
-    <t>on $13,463.64 collected</t>
+    <t>on $12,363.64 collected</t>
   </si>
   <si>
     <t>Baseline reorders (10%)</t>
   </si>
   <si>
-    <t>on $6,936.36 collected</t>
+    <t>on $8,036.36 collected</t>
   </si>
   <si>
     <t>Spiff — 2 new acct(s) × $750</t>
@@ -73,7 +79,7 @@
     <t>vs. standard waterfall would have paid</t>
   </si>
   <si>
-    <t>Uplift: $6746.59</t>
+    <t>Uplift: $6239.09</t>
   </si>
   <si>
     <t>Account / Date</t>
@@ -142,12 +148,6 @@
     <t>ORD-EPL-1189</t>
   </si>
   <si>
-    <t>Smith Performance Equine</t>
-  </si>
-  <si>
-    <t>ORD-EPL-1183</t>
-  </si>
-  <si>
     <t>Signature Equine Hospital</t>
   </si>
   <si>
@@ -157,13 +157,10 @@
     <t>Elgin Equine</t>
   </si>
   <si>
+    <t>ORD-EPL-1185</t>
+  </si>
+  <si>
     <t>ORD-EPL-1129</t>
-  </si>
-  <si>
-    <t>Panorama Equine Medical and Surgical Center</t>
-  </si>
-  <si>
-    <t>ORD-EPL-1157</t>
   </si>
   <si>
     <t>Buffalo Veterinary Clinic PC</t>
@@ -229,6 +226,11 @@
     <font>
       <b/>
       <color rgb="0F5E4F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="0F5E4F"/>
       <sz val="12"/>
     </font>
     <font>
@@ -257,11 +259,6 @@
     <font>
       <b/>
       <color rgb="FFFFFF"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="0F5E4F"/>
       <sz val="10"/>
     </font>
     <font>
@@ -306,7 +303,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -314,23 +311,24 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="9" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="10" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -690,7 +688,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H55"/>
+  <dimension ref="A1:H50"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
@@ -711,7 +709,7 @@
         <v>1</v>
       </c>
       <c r="H1" s="3">
-        <v>9161.59</v>
+        <v>8414.09</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
@@ -736,549 +734,515 @@
         <v>7</v>
       </c>
     </row>
+    <row r="4" spans="7:8" x14ac:dyDescent="0.25">
+      <c r="G4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" s="6" t="s">
-        <v>8</v>
+      <c r="A5" s="7" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" s="7">
+        <v>11</v>
+      </c>
+      <c r="B6" s="8">
         <v>78375</v>
       </c>
-      <c r="C6" s="8" t="s">
-        <v>10</v>
+      <c r="C6" s="9" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7" s="9">
-        <v>3285</v>
-      </c>
-      <c r="C7" s="10" t="s">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="B7" s="10">
+        <v>2565</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B8" s="9">
-        <v>1682.95</v>
-      </c>
-      <c r="C8" s="10" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="B8" s="10">
+        <v>1545.45</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B9" s="9">
-        <v>693.64</v>
-      </c>
-      <c r="C9" s="10" t="s">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="B9" s="10">
+        <v>803.64</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B10" s="9">
+        <v>19</v>
+      </c>
+      <c r="B10" s="10">
         <v>1500</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B11" s="9">
+        <v>20</v>
+      </c>
+      <c r="B11" s="10">
         <v>2000</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="B12" s="11">
-        <v>2415</v>
-      </c>
-      <c r="C12" s="12" t="s">
-        <v>20</v>
+      <c r="A12" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="B12" s="12">
+        <v>2175</v>
+      </c>
+      <c r="C12" s="13" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="B14" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="C14" s="13" t="s">
+      <c r="A14" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="D14" s="13" t="s">
+      <c r="B14" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="E14" s="13" t="s">
+      <c r="C14" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="F14" s="14" t="s">
+      <c r="D14" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="G14" s="14" t="s">
+      <c r="E14" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="H14" s="14" t="s">
+      <c r="F14" s="15" t="s">
         <v>28</v>
       </c>
+      <c r="G14" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="H14" s="15" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="F15" s="16">
+      <c r="A15" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="F15" s="17">
         <v>10500</v>
       </c>
-      <c r="H15" s="17">
+      <c r="H15" s="18">
         <v>1575</v>
       </c>
     </row>
     <row r="16" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B16" s="18">
+      <c r="B16" s="19">
         <v>46262.5</v>
       </c>
-      <c r="C16" s="19" t="s">
-        <v>30</v>
+      <c r="C16" s="20" t="s">
+        <v>32</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="F16" s="20">
+        <v>33</v>
+      </c>
+      <c r="F16" s="21">
         <v>10500</v>
       </c>
-      <c r="G16" s="21">
+      <c r="G16" s="22">
         <v>0.15</v>
       </c>
-      <c r="H16" s="22">
+      <c r="H16" s="23">
         <v>1575</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="F18" s="16">
+      <c r="A18" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="F18" s="17">
         <v>7200</v>
       </c>
-      <c r="H18" s="17">
+      <c r="H18" s="18">
         <v>829.09</v>
       </c>
     </row>
     <row r="19" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B19" s="18">
+      <c r="B19" s="19">
         <v>46254.5</v>
       </c>
-      <c r="C19" s="19" t="s">
-        <v>30</v>
+      <c r="C19" s="20" t="s">
+        <v>32</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="F19" s="20">
+        <v>35</v>
+      </c>
+      <c r="F19" s="21">
         <v>1800</v>
       </c>
-      <c r="G19" s="21">
+      <c r="G19" s="22">
         <v>0.11515151515151516</v>
       </c>
-      <c r="H19" s="22">
+      <c r="H19" s="23">
         <v>207.27</v>
       </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B20" s="18">
+      <c r="B20" s="19">
         <v>46254.5</v>
       </c>
-      <c r="C20" s="19" t="s">
-        <v>30</v>
+      <c r="C20" s="20" t="s">
+        <v>32</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="F20" s="20">
+        <v>36</v>
+      </c>
+      <c r="F20" s="21">
         <v>2400</v>
       </c>
-      <c r="G20" s="21">
+      <c r="G20" s="22">
         <v>0.11515151515151516</v>
       </c>
-      <c r="H20" s="22">
+      <c r="H20" s="23">
         <v>276.36</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B21" s="18">
+      <c r="B21" s="19">
         <v>46261.5</v>
       </c>
-      <c r="C21" s="19" t="s">
-        <v>30</v>
+      <c r="C21" s="20" t="s">
+        <v>32</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="F21" s="20">
+        <v>37</v>
+      </c>
+      <c r="F21" s="21">
         <v>600</v>
       </c>
-      <c r="G21" s="21">
+      <c r="G21" s="22">
         <v>0.11515151515151516</v>
       </c>
-      <c r="H21" s="22">
+      <c r="H21" s="23">
         <v>69.09</v>
       </c>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B22" s="18">
+      <c r="B22" s="19">
         <v>46261.5</v>
       </c>
-      <c r="C22" s="19" t="s">
-        <v>30</v>
+      <c r="C22" s="20" t="s">
+        <v>32</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="F22" s="20">
+        <v>38</v>
+      </c>
+      <c r="F22" s="21">
         <v>2400</v>
       </c>
-      <c r="G22" s="21">
+      <c r="G22" s="22">
         <v>0.11515151515151516</v>
       </c>
-      <c r="H22" s="22">
+      <c r="H22" s="23">
         <v>276.36</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="F24" s="16">
+      <c r="A24" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="F24" s="17">
         <v>4800</v>
       </c>
-      <c r="H24" s="17">
+      <c r="H24" s="18">
         <v>480</v>
       </c>
     </row>
     <row r="25" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B25" s="18">
+      <c r="B25" s="19">
         <v>46239.5</v>
       </c>
-      <c r="C25" s="19" t="s">
-        <v>30</v>
+      <c r="C25" s="20" t="s">
+        <v>32</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F25" s="20">
+        <v>40</v>
+      </c>
+      <c r="F25" s="21">
         <v>4800</v>
       </c>
-      <c r="G25" s="21">
+      <c r="G25" s="22">
         <v>0.1</v>
       </c>
-      <c r="H25" s="22">
+      <c r="H25" s="23">
         <v>480</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="F27" s="16">
+      <c r="A27" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="F27" s="17">
         <v>4800</v>
       </c>
-      <c r="H27" s="17">
+      <c r="H27" s="18">
         <v>720</v>
       </c>
     </row>
     <row r="28" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B28" s="18">
+      <c r="B28" s="19">
         <v>46254.5</v>
       </c>
-      <c r="C28" s="19" t="s">
-        <v>30</v>
+      <c r="C28" s="20" t="s">
+        <v>32</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="F28" s="20">
+        <v>42</v>
+      </c>
+      <c r="F28" s="21">
         <v>4800</v>
       </c>
-      <c r="G28" s="21">
+      <c r="G28" s="22">
         <v>0.15</v>
       </c>
-      <c r="H28" s="22">
+      <c r="H28" s="23">
         <v>720</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" s="15" t="s">
-        <v>41</v>
-      </c>
-      <c r="F30" s="16">
+      <c r="A30" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="F30" s="17">
         <v>4800</v>
       </c>
-      <c r="H30" s="17">
+      <c r="H30" s="18">
         <v>576</v>
       </c>
     </row>
     <row r="31" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B31" s="18">
+      <c r="B31" s="19">
         <v>46254.5</v>
       </c>
-      <c r="C31" s="19" t="s">
-        <v>30</v>
+      <c r="C31" s="20" t="s">
+        <v>32</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="F31" s="20">
+        <v>44</v>
+      </c>
+      <c r="F31" s="21">
         <v>4800</v>
       </c>
-      <c r="G31" s="21">
+      <c r="G31" s="22">
         <v>0.12000000000000001</v>
       </c>
-      <c r="H31" s="22">
+      <c r="H31" s="23">
         <v>576</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A33" s="15" t="s">
-        <v>43</v>
-      </c>
-      <c r="F33" s="16">
+      <c r="A33" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="F33" s="17">
         <v>4800</v>
       </c>
-      <c r="H33" s="17">
-        <v>720</v>
+      <c r="H33" s="18">
+        <v>584</v>
       </c>
     </row>
     <row r="34" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B34" s="18">
+      <c r="B34" s="19">
         <v>46259.5</v>
       </c>
-      <c r="C34" s="19" t="s">
-        <v>30</v>
+      <c r="C34" s="20" t="s">
+        <v>32</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="F34" s="20">
+        <v>46</v>
+      </c>
+      <c r="F34" s="21">
         <v>4800</v>
       </c>
-      <c r="G34" s="21">
+      <c r="G34" s="22">
+        <v>0.12166666666666666</v>
+      </c>
+      <c r="H34" s="23">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="F36" s="17">
+        <v>3600</v>
+      </c>
+      <c r="H36" s="18">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="37" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B37" s="19">
+        <v>46254.5</v>
+      </c>
+      <c r="C37" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="F37" s="21">
+        <v>1800</v>
+      </c>
+      <c r="G37" s="22">
+        <v>0.1</v>
+      </c>
+      <c r="H37" s="23">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="38" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B38" s="19">
+        <v>46254.5</v>
+      </c>
+      <c r="C38" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="F38" s="21">
+        <v>1800</v>
+      </c>
+      <c r="G38" s="22">
+        <v>0.1</v>
+      </c>
+      <c r="H38" s="23">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="F40" s="17">
+        <v>1200</v>
+      </c>
+      <c r="H40" s="18">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="41" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B41" s="19">
+        <v>46244.5</v>
+      </c>
+      <c r="C41" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F41" s="21">
+        <v>1200</v>
+      </c>
+      <c r="G41" s="22">
+        <v>0.1</v>
+      </c>
+      <c r="H41" s="23">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="F43" s="17">
+        <v>1200</v>
+      </c>
+      <c r="H43" s="18">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="44" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B44" s="19">
+        <v>46262.5</v>
+      </c>
+      <c r="C44" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="F44" s="21">
+        <v>1200</v>
+      </c>
+      <c r="G44" s="22">
         <v>0.15</v>
       </c>
-      <c r="H34" s="22">
-        <v>720</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A36" s="15" t="s">
-        <v>45</v>
-      </c>
-      <c r="F36" s="16">
-        <v>4800</v>
-      </c>
-      <c r="H36" s="17">
-        <v>584</v>
-      </c>
-    </row>
-    <row r="37" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B37" s="18">
-        <v>46259.5</v>
-      </c>
-      <c r="C37" s="19" t="s">
-        <v>30</v>
-      </c>
-      <c r="E37" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="F37" s="20">
-        <v>4800</v>
-      </c>
-      <c r="G37" s="21">
-        <v>0.12166666666666666</v>
-      </c>
-      <c r="H37" s="22">
-        <v>584</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A39" s="15" t="s">
-        <v>47</v>
-      </c>
-      <c r="F39" s="16">
-        <v>1800</v>
-      </c>
-      <c r="H39" s="17">
+      <c r="H44" s="23">
         <v>180</v>
       </c>
     </row>
-    <row r="40" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B40" s="18">
-        <v>46254.5</v>
-      </c>
-      <c r="C40" s="19" t="s">
-        <v>30</v>
-      </c>
-      <c r="E40" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="F40" s="20">
-        <v>1800</v>
-      </c>
-      <c r="G40" s="21">
-        <v>0.1</v>
-      </c>
-      <c r="H40" s="22">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A42" s="15" t="s">
-        <v>49</v>
-      </c>
-      <c r="F42" s="16">
-        <v>1800</v>
-      </c>
-      <c r="H42" s="17">
-        <v>207.5</v>
-      </c>
-    </row>
-    <row r="43" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B43" s="18">
-        <v>46259.5</v>
-      </c>
-      <c r="C43" s="19" t="s">
-        <v>30</v>
-      </c>
-      <c r="E43" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="F43" s="20">
-        <v>1800</v>
-      </c>
-      <c r="G43" s="21">
-        <v>0.11527777777777777</v>
-      </c>
-      <c r="H43" s="22">
-        <v>207.5</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A45" s="15" t="s">
-        <v>51</v>
-      </c>
-      <c r="F45" s="16">
-        <v>1200</v>
-      </c>
-      <c r="H45" s="17">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="46" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B46" s="18">
-        <v>46244.5</v>
-      </c>
-      <c r="C46" s="19" t="s">
-        <v>30</v>
-      </c>
-      <c r="E46" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="F46" s="20">
-        <v>1200</v>
-      </c>
-      <c r="G46" s="21">
-        <v>0.1</v>
-      </c>
-      <c r="H46" s="22">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A48" s="15" t="s">
-        <v>53</v>
-      </c>
-      <c r="F48" s="16">
-        <v>1200</v>
-      </c>
-      <c r="H48" s="17">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="49" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B49" s="18">
-        <v>46262.5</v>
-      </c>
-      <c r="C49" s="19" t="s">
-        <v>30</v>
-      </c>
-      <c r="E49" s="2" t="s">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="F49" s="20">
-        <v>1200</v>
-      </c>
-      <c r="G49" s="21">
+      <c r="F46" s="17">
+        <v>600</v>
+      </c>
+      <c r="H46" s="18">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="47" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B47" s="19">
+        <v>46252.5</v>
+      </c>
+      <c r="C47" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="F47" s="21">
+        <v>600</v>
+      </c>
+      <c r="G47" s="22">
         <v>0.15</v>
       </c>
-      <c r="H49" s="22">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A51" s="15" t="s">
-        <v>55</v>
-      </c>
-      <c r="F51" s="16">
-        <v>600</v>
-      </c>
-      <c r="H51" s="17">
+      <c r="H47" s="23">
         <v>90</v>
       </c>
     </row>
-    <row r="52" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B52" s="18">
-        <v>46252.5</v>
-      </c>
-      <c r="C52" s="19" t="s">
-        <v>30</v>
-      </c>
-      <c r="E52" s="2" t="s">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50" s="24" t="s">
         <v>56</v>
       </c>
-      <c r="F52" s="20">
-        <v>600</v>
-      </c>
-      <c r="G52" s="21">
-        <v>0.15</v>
-      </c>
-      <c r="H52" s="22">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A55" s="23" t="s">
-        <v>57</v>
-      </c>
-      <c r="F55" s="24">
+      <c r="F50" s="25">
         <v>78375</v>
       </c>
-      <c r="H55" s="25">
-        <v>9161.59</v>
+      <c r="H50" s="26">
+        <v>8414.09</v>
       </c>
     </row>
   </sheetData>

--- a/commission/karin/2026-08.xlsx
+++ b/commission/karin/2026-08.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="61">
   <si>
     <t>Equine Performance Labs, LLC</t>
   </si>
@@ -55,19 +55,19 @@
     <t>New / Reactivated (15%)</t>
   </si>
   <si>
-    <t>on $17,100.00 collected</t>
+    <t>on $21,900.00 collected</t>
   </si>
   <si>
     <t>Growth above baseline (12.5%)</t>
   </si>
   <si>
-    <t>on $12,363.64 collected</t>
+    <t>on $13,463.64 collected</t>
   </si>
   <si>
     <t>Baseline reorders (10%)</t>
   </si>
   <si>
-    <t>on $8,036.36 collected</t>
+    <t>on $8,736.36 collected</t>
   </si>
   <si>
     <t>Spiff — 2 new acct(s) × $750</t>
@@ -79,7 +79,7 @@
     <t>vs. standard waterfall would have paid</t>
   </si>
   <si>
-    <t>Uplift: $6239.09</t>
+    <t>Uplift: $6836.59</t>
   </si>
   <si>
     <t>Account / Date</t>
@@ -148,6 +148,12 @@
     <t>ORD-EPL-1189</t>
   </si>
   <si>
+    <t>Smith Performance Equine</t>
+  </si>
+  <si>
+    <t>ORD-EPL-1183</t>
+  </si>
+  <si>
     <t>Signature Equine Hospital</t>
   </si>
   <si>
@@ -161,6 +167,12 @@
   </si>
   <si>
     <t>ORD-EPL-1129</t>
+  </si>
+  <si>
+    <t>Panorama Equine Medical and Surgical Center</t>
+  </si>
+  <si>
+    <t>ORD-EPL-1157</t>
   </si>
   <si>
     <t>Buffalo Veterinary Clinic PC</t>
@@ -688,7 +700,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H50"/>
+  <dimension ref="A1:H56"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
@@ -709,7 +721,7 @@
         <v>1</v>
       </c>
       <c r="H1" s="3">
-        <v>8414.09</v>
+        <v>9341.59</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
@@ -763,7 +775,7 @@
         <v>13</v>
       </c>
       <c r="B7" s="10">
-        <v>2565</v>
+        <v>3285</v>
       </c>
       <c r="C7" s="11" t="s">
         <v>14</v>
@@ -774,7 +786,7 @@
         <v>15</v>
       </c>
       <c r="B8" s="10">
-        <v>1545.45</v>
+        <v>1682.95</v>
       </c>
       <c r="C8" s="11" t="s">
         <v>16</v>
@@ -785,7 +797,7 @@
         <v>17</v>
       </c>
       <c r="B9" s="10">
-        <v>803.64</v>
+        <v>873.64</v>
       </c>
       <c r="C9" s="11" t="s">
         <v>18</v>
@@ -812,7 +824,7 @@
         <v>21</v>
       </c>
       <c r="B12" s="12">
-        <v>2175</v>
+        <v>2505</v>
       </c>
       <c r="C12" s="13" t="s">
         <v>22</v>
@@ -1067,7 +1079,7 @@
         <v>4800</v>
       </c>
       <c r="H33" s="18">
-        <v>584</v>
+        <v>720</v>
       </c>
     </row>
     <row r="34" spans="2:8" x14ac:dyDescent="0.25">
@@ -1084,10 +1096,10 @@
         <v>4800</v>
       </c>
       <c r="G34" s="22">
-        <v>0.12166666666666666</v>
+        <v>0.15</v>
       </c>
       <c r="H34" s="23">
-        <v>584</v>
+        <v>720</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
@@ -1095,15 +1107,15 @@
         <v>47</v>
       </c>
       <c r="F36" s="17">
-        <v>3600</v>
+        <v>4800</v>
       </c>
       <c r="H36" s="18">
-        <v>360</v>
+        <v>584</v>
       </c>
     </row>
     <row r="37" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B37" s="19">
-        <v>46254.5</v>
+        <v>46259.5</v>
       </c>
       <c r="C37" s="20" t="s">
         <v>32</v>
@@ -1112,49 +1124,49 @@
         <v>48</v>
       </c>
       <c r="F37" s="21">
+        <v>4800</v>
+      </c>
+      <c r="G37" s="22">
+        <v>0.12166666666666666</v>
+      </c>
+      <c r="H37" s="23">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="F39" s="17">
+        <v>3600</v>
+      </c>
+      <c r="H39" s="18">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="40" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B40" s="19">
+        <v>46254.5</v>
+      </c>
+      <c r="C40" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="F40" s="21">
         <v>1800</v>
       </c>
-      <c r="G37" s="22">
+      <c r="G40" s="22">
         <v>0.1</v>
       </c>
-      <c r="H37" s="23">
+      <c r="H40" s="23">
         <v>180</v>
-      </c>
-    </row>
-    <row r="38" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B38" s="19">
-        <v>46254.5</v>
-      </c>
-      <c r="C38" s="20" t="s">
-        <v>32</v>
-      </c>
-      <c r="E38" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="F38" s="21">
-        <v>1800</v>
-      </c>
-      <c r="G38" s="22">
-        <v>0.1</v>
-      </c>
-      <c r="H38" s="23">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A40" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="F40" s="17">
-        <v>1200</v>
-      </c>
-      <c r="H40" s="18">
-        <v>120</v>
       </c>
     </row>
     <row r="41" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B41" s="19">
-        <v>46244.5</v>
+        <v>46254.5</v>
       </c>
       <c r="C41" s="20" t="s">
         <v>32</v>
@@ -1163,13 +1175,13 @@
         <v>51</v>
       </c>
       <c r="F41" s="21">
-        <v>1200</v>
+        <v>1800</v>
       </c>
       <c r="G41" s="22">
         <v>0.1</v>
       </c>
       <c r="H41" s="23">
-        <v>120</v>
+        <v>180</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
@@ -1177,15 +1189,15 @@
         <v>52</v>
       </c>
       <c r="F43" s="17">
-        <v>1200</v>
+        <v>1800</v>
       </c>
       <c r="H43" s="18">
-        <v>180</v>
+        <v>207.5</v>
       </c>
     </row>
     <row r="44" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B44" s="19">
-        <v>46262.5</v>
+        <v>46259.5</v>
       </c>
       <c r="C44" s="20" t="s">
         <v>32</v>
@@ -1194,13 +1206,13 @@
         <v>53</v>
       </c>
       <c r="F44" s="21">
-        <v>1200</v>
+        <v>1800</v>
       </c>
       <c r="G44" s="22">
-        <v>0.15</v>
+        <v>0.11527777777777777</v>
       </c>
       <c r="H44" s="23">
-        <v>180</v>
+        <v>207.5</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
@@ -1208,15 +1220,15 @@
         <v>54</v>
       </c>
       <c r="F46" s="17">
-        <v>600</v>
+        <v>1200</v>
       </c>
       <c r="H46" s="18">
-        <v>90</v>
+        <v>120</v>
       </c>
     </row>
     <row r="47" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B47" s="19">
-        <v>46252.5</v>
+        <v>46244.5</v>
       </c>
       <c r="C47" s="20" t="s">
         <v>32</v>
@@ -1225,24 +1237,86 @@
         <v>55</v>
       </c>
       <c r="F47" s="21">
+        <v>1200</v>
+      </c>
+      <c r="G47" s="22">
+        <v>0.1</v>
+      </c>
+      <c r="H47" s="23">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="F49" s="17">
+        <v>1200</v>
+      </c>
+      <c r="H49" s="18">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="50" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B50" s="19">
+        <v>46262.5</v>
+      </c>
+      <c r="C50" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="F50" s="21">
+        <v>1200</v>
+      </c>
+      <c r="G50" s="22">
+        <v>0.15</v>
+      </c>
+      <c r="H50" s="23">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A52" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="F52" s="17">
         <v>600</v>
       </c>
-      <c r="G47" s="22">
+      <c r="H52" s="18">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="53" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B53" s="19">
+        <v>46252.5</v>
+      </c>
+      <c r="C53" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="F53" s="21">
+        <v>600</v>
+      </c>
+      <c r="G53" s="22">
         <v>0.15</v>
       </c>
-      <c r="H47" s="23">
+      <c r="H53" s="23">
         <v>90</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A50" s="24" t="s">
-        <v>56</v>
-      </c>
-      <c r="F50" s="25">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56" s="24" t="s">
+        <v>60</v>
+      </c>
+      <c r="F56" s="25">
         <v>78375</v>
       </c>
-      <c r="H50" s="26">
-        <v>8414.09</v>
+      <c r="H56" s="26">
+        <v>9341.59</v>
       </c>
     </row>
   </sheetData>

--- a/commission/karin/2026-08.xlsx
+++ b/commission/karin/2026-08.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="62">
   <si>
     <t>Equine Performance Labs, LLC</t>
   </si>
@@ -74,6 +74,9 @@
   </si>
   <si>
     <t>Breadth bonus — 8 accts ≥20%</t>
+  </si>
+  <si>
+    <t>Qualifying: Tanner Equine, Santa Lucia Farm, Signature Equine Hospital, Panorama Equine Medical and Surgical Center</t>
   </si>
   <si>
     <t>vs. standard waterfall would have paid</t>
@@ -811,54 +814,62 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>20</v>
       </c>
       <c r="B11" s="10">
         <v>2000</v>
       </c>
+      <c r="C11" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="D11" s="11"/>
+      <c r="E11" s="11"/>
+      <c r="F11" s="11"/>
+      <c r="G11" s="11"/>
+      <c r="H11" s="11"/>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B12" s="12">
         <v>2505</v>
       </c>
       <c r="C12" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="14" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B14" s="14" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D14" s="14" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E14" s="14" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F14" s="15" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G14" s="15" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H14" s="15" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="16" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F15" s="17">
         <v>10500</v>
@@ -872,10 +883,10 @@
         <v>46262.5</v>
       </c>
       <c r="C16" s="20" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F16" s="21">
         <v>10500</v>
@@ -889,7 +900,7 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="16" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F18" s="17">
         <v>7200</v>
@@ -903,10 +914,10 @@
         <v>46254.5</v>
       </c>
       <c r="C19" s="20" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F19" s="21">
         <v>1800</v>
@@ -923,10 +934,10 @@
         <v>46254.5</v>
       </c>
       <c r="C20" s="20" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F20" s="21">
         <v>2400</v>
@@ -943,10 +954,10 @@
         <v>46261.5</v>
       </c>
       <c r="C21" s="20" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F21" s="21">
         <v>600</v>
@@ -963,10 +974,10 @@
         <v>46261.5</v>
       </c>
       <c r="C22" s="20" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F22" s="21">
         <v>2400</v>
@@ -980,7 +991,7 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="16" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F24" s="17">
         <v>4800</v>
@@ -994,10 +1005,10 @@
         <v>46239.5</v>
       </c>
       <c r="C25" s="20" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F25" s="21">
         <v>4800</v>
@@ -1011,7 +1022,7 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="16" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F27" s="17">
         <v>4800</v>
@@ -1025,10 +1036,10 @@
         <v>46254.5</v>
       </c>
       <c r="C28" s="20" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F28" s="21">
         <v>4800</v>
@@ -1042,7 +1053,7 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="16" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F30" s="17">
         <v>4800</v>
@@ -1056,10 +1067,10 @@
         <v>46254.5</v>
       </c>
       <c r="C31" s="20" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F31" s="21">
         <v>4800</v>
@@ -1073,7 +1084,7 @@
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="16" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F33" s="17">
         <v>4800</v>
@@ -1087,10 +1098,10 @@
         <v>46259.5</v>
       </c>
       <c r="C34" s="20" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F34" s="21">
         <v>4800</v>
@@ -1104,7 +1115,7 @@
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="16" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F36" s="17">
         <v>4800</v>
@@ -1118,10 +1129,10 @@
         <v>46259.5</v>
       </c>
       <c r="C37" s="20" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F37" s="21">
         <v>4800</v>
@@ -1135,7 +1146,7 @@
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" s="16" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F39" s="17">
         <v>3600</v>
@@ -1149,10 +1160,10 @@
         <v>46254.5</v>
       </c>
       <c r="C40" s="20" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F40" s="21">
         <v>1800</v>
@@ -1169,10 +1180,10 @@
         <v>46254.5</v>
       </c>
       <c r="C41" s="20" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F41" s="21">
         <v>1800</v>
@@ -1186,7 +1197,7 @@
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" s="16" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F43" s="17">
         <v>1800</v>
@@ -1200,10 +1211,10 @@
         <v>46259.5</v>
       </c>
       <c r="C44" s="20" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F44" s="21">
         <v>1800</v>
@@ -1217,7 +1228,7 @@
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" s="16" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F46" s="17">
         <v>1200</v>
@@ -1231,10 +1242,10 @@
         <v>46244.5</v>
       </c>
       <c r="C47" s="20" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F47" s="21">
         <v>1200</v>
@@ -1248,7 +1259,7 @@
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" s="16" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F49" s="17">
         <v>1200</v>
@@ -1262,10 +1273,10 @@
         <v>46262.5</v>
       </c>
       <c r="C50" s="20" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F50" s="21">
         <v>1200</v>
@@ -1279,7 +1290,7 @@
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" s="16" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F52" s="17">
         <v>600</v>
@@ -1293,10 +1304,10 @@
         <v>46252.5</v>
       </c>
       <c r="C53" s="20" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F53" s="21">
         <v>600</v>
@@ -1310,7 +1321,7 @@
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" s="24" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F56" s="25">
         <v>78375</v>
@@ -1320,6 +1331,9 @@
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="C11:H11"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>

--- a/commission/karin/2026-08.xlsx
+++ b/commission/karin/2026-08.xlsx
@@ -5,13 +5,14 @@
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
     <sheet sheetId="1" name="August 2026-08" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="Invoiced This Month" state="visible" r:id="rId5"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="121">
   <si>
     <t>Equine Performance Labs, LLC</t>
   </si>
@@ -197,6 +198,183 @@
   </si>
   <si>
     <t>GRAND TOTAL</t>
+  </si>
+  <si>
+    <t>Invoiced This Month — Karin Williamson — August 2026</t>
+  </si>
+  <si>
+    <t>Every invoice you wrote this month (paid or unpaid). Commission math comes from Tab 1 — this sheet is for visibility only.</t>
+  </si>
+  <si>
+    <t>INV#</t>
+  </si>
+  <si>
+    <t>Customer</t>
+  </si>
+  <si>
+    <t>Vials</t>
+  </si>
+  <si>
+    <t>Base</t>
+  </si>
+  <si>
+    <t>Discount</t>
+  </si>
+  <si>
+    <t>Final</t>
+  </si>
+  <si>
+    <t>Commissionable</t>
+  </si>
+  <si>
+    <t>Paid</t>
+  </si>
+  <si>
+    <t>Payment Date</t>
+  </si>
+  <si>
+    <t>Open Bal</t>
+  </si>
+  <si>
+    <t>Promo</t>
+  </si>
+  <si>
+    <t>ORD-EPL-1162</t>
+  </si>
+  <si>
+    <t>Republic of Texas Equine Medical Center</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>FREE_VIALS</t>
+  </si>
+  <si>
+    <t>ORD-EPL-1161</t>
+  </si>
+  <si>
+    <t>ORD-EPL-1160</t>
+  </si>
+  <si>
+    <t>David M Dutton, DVM PC</t>
+  </si>
+  <si>
+    <t>ORD-EPL-1159</t>
+  </si>
+  <si>
+    <t>ORD-EPL-1166</t>
+  </si>
+  <si>
+    <t>Mid-South Equine Sports Medicine &amp; Surgery</t>
+  </si>
+  <si>
+    <t>ORD-EPL-1165</t>
+  </si>
+  <si>
+    <t>SAMPLE26</t>
+  </si>
+  <si>
+    <t>ORD-EPL-1169</t>
+  </si>
+  <si>
+    <t>Pioneer Equine Hospital</t>
+  </si>
+  <si>
+    <t>ORD-EPL-1175</t>
+  </si>
+  <si>
+    <t>ORD-EPL-1174</t>
+  </si>
+  <si>
+    <t>Outlaw Equine</t>
+  </si>
+  <si>
+    <t>ORD-EPL-1173</t>
+  </si>
+  <si>
+    <t>ORD-EPL-1181</t>
+  </si>
+  <si>
+    <t>ORD-EPL-1179</t>
+  </si>
+  <si>
+    <t>ORD-EPL-1184</t>
+  </si>
+  <si>
+    <t>ORD-EPL-1190</t>
+  </si>
+  <si>
+    <t>ORD-EPL-1198</t>
+  </si>
+  <si>
+    <t>Double X Veterinary Services</t>
+  </si>
+  <si>
+    <t>ORD-EPL-1197</t>
+  </si>
+  <si>
+    <t>ORD-EPL-1201</t>
+  </si>
+  <si>
+    <t>Mt. Laramie Veterinary Services</t>
+  </si>
+  <si>
+    <t>ORD-EPL-1205</t>
+  </si>
+  <si>
+    <t>Equine Athlete Veterinary Services - Simpsonville, KY</t>
+  </si>
+  <si>
+    <t>ORD-EPL-1204</t>
+  </si>
+  <si>
+    <t>ORD-EPL-1211</t>
+  </si>
+  <si>
+    <t>ORD-EPL-1210</t>
+  </si>
+  <si>
+    <t>ORD-EPL-1214</t>
+  </si>
+  <si>
+    <t>ORD-EPL-1213</t>
+  </si>
+  <si>
+    <t>La Feliz Montana Ranch</t>
+  </si>
+  <si>
+    <t>ORD-EPL-1212</t>
+  </si>
+  <si>
+    <t>Equine Sports Medicine &amp; Surgery</t>
+  </si>
+  <si>
+    <t>ORD-EPL-1218</t>
+  </si>
+  <si>
+    <t>MVP Equine</t>
+  </si>
+  <si>
+    <t>ORD-EPL-1217</t>
+  </si>
+  <si>
+    <t>Desert Pines Equine</t>
+  </si>
+  <si>
+    <t>ORD-EPL-1216</t>
+  </si>
+  <si>
+    <t>ORD-EPL-1215</t>
+  </si>
+  <si>
+    <t>ORD-EPL-1220</t>
+  </si>
+  <si>
+    <t>RD Equine</t>
+  </si>
+  <si>
+    <t>40 invoices</t>
   </si>
 </sst>
 </file>
@@ -209,7 +387,7 @@
     <numFmt numFmtId="166" formatCode="m/d/yyyy"/>
     <numFmt numFmtId="167" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="27" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -287,6 +465,45 @@
       <b/>
       <sz val="12"/>
     </font>
+    <font>
+      <b/>
+      <color rgb="123F35"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <i/>
+      <color rgb="7A7974"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <color rgb="DA7101"/>
+    </font>
+    <font>
+      <b/>
+    </font>
+    <font>
+      <color rgb="7A7974"/>
+    </font>
+    <font>
+      <color rgb="964219"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="DA7101"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="123F35"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="0F5E4F"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="964219"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -318,7 +535,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -362,6 +579,48 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -1337,4 +1596,1629 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:L47"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="15" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="3" max="3" width="36" customWidth="1"/>
+    <col min="4" max="4" width="7" customWidth="1"/>
+    <col min="5" max="6" width="12" customWidth="1"/>
+    <col min="7" max="7" width="14" customWidth="1"/>
+    <col min="8" max="8" width="15" customWidth="1"/>
+    <col min="9" max="10" width="13" customWidth="1"/>
+    <col min="11" max="11" width="12" customWidth="1"/>
+    <col min="12" max="12" width="14" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" s="27" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" s="28" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A5" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="B5" s="29" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="D5" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="E5" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="F5" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="G5" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="H5" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="I5" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="J5" s="29" t="s">
+        <v>72</v>
+      </c>
+      <c r="K5" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="L5" s="29" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A6" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="B6" s="30">
+        <v>46237.5</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D6" s="31">
+        <v>2</v>
+      </c>
+      <c r="E6" s="21">
+        <v>1650</v>
+      </c>
+      <c r="F6" s="32">
+        <v>1650</v>
+      </c>
+      <c r="G6" s="33">
+        <v>0</v>
+      </c>
+      <c r="H6" s="21">
+        <v>0</v>
+      </c>
+      <c r="I6" s="34">
+        <v>0</v>
+      </c>
+      <c r="J6" s="30" t="s">
+        <v>77</v>
+      </c>
+      <c r="K6" s="34">
+        <v>0</v>
+      </c>
+      <c r="L6" s="35" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A7" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="B7" s="30">
+        <v>46237.5</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D7" s="31">
+        <v>8</v>
+      </c>
+      <c r="E7" s="21">
+        <v>6600</v>
+      </c>
+      <c r="F7" s="32">
+        <v>1800</v>
+      </c>
+      <c r="G7" s="33">
+        <v>4800</v>
+      </c>
+      <c r="H7" s="21">
+        <v>4800</v>
+      </c>
+      <c r="I7" s="23">
+        <v>4800</v>
+      </c>
+      <c r="J7" s="30">
+        <v>46275.5</v>
+      </c>
+      <c r="K7" s="34">
+        <v>0</v>
+      </c>
+      <c r="L7" s="35" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A8" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="B8" s="30">
+        <v>46237.5</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="D8" s="31">
+        <v>2</v>
+      </c>
+      <c r="E8" s="21">
+        <v>1650</v>
+      </c>
+      <c r="F8" s="32">
+        <v>1650</v>
+      </c>
+      <c r="G8" s="33">
+        <v>0</v>
+      </c>
+      <c r="H8" s="21">
+        <v>0</v>
+      </c>
+      <c r="I8" s="34">
+        <v>0</v>
+      </c>
+      <c r="J8" s="30" t="s">
+        <v>77</v>
+      </c>
+      <c r="K8" s="34">
+        <v>0</v>
+      </c>
+      <c r="L8" s="35" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A9" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="B9" s="30">
+        <v>46237.5</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="D9" s="31">
+        <v>8</v>
+      </c>
+      <c r="E9" s="21">
+        <v>6600</v>
+      </c>
+      <c r="F9" s="32">
+        <v>1800</v>
+      </c>
+      <c r="G9" s="33">
+        <v>4800</v>
+      </c>
+      <c r="H9" s="21">
+        <v>4800</v>
+      </c>
+      <c r="I9" s="23">
+        <v>4800</v>
+      </c>
+      <c r="J9" s="30">
+        <v>46274.5</v>
+      </c>
+      <c r="K9" s="34">
+        <v>0</v>
+      </c>
+      <c r="L9" s="35" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A10" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B10" s="30">
+        <v>46237.5</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D10" s="31">
+        <v>4</v>
+      </c>
+      <c r="E10" s="21">
+        <v>3300</v>
+      </c>
+      <c r="F10" s="32">
+        <v>900</v>
+      </c>
+      <c r="G10" s="33">
+        <v>2400</v>
+      </c>
+      <c r="H10" s="21">
+        <v>2400</v>
+      </c>
+      <c r="I10" s="23">
+        <v>2400</v>
+      </c>
+      <c r="J10" s="30">
+        <v>46261.5</v>
+      </c>
+      <c r="K10" s="34">
+        <v>0</v>
+      </c>
+      <c r="L10" s="35" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A11" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B11" s="30">
+        <v>46237.5</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="D11" s="31">
+        <v>3</v>
+      </c>
+      <c r="E11" s="21">
+        <v>2475</v>
+      </c>
+      <c r="F11" s="32">
+        <v>675</v>
+      </c>
+      <c r="G11" s="33">
+        <v>1800</v>
+      </c>
+      <c r="H11" s="21">
+        <v>1800</v>
+      </c>
+      <c r="I11" s="23">
+        <v>1800</v>
+      </c>
+      <c r="J11" s="30">
+        <v>46259.5</v>
+      </c>
+      <c r="K11" s="34">
+        <v>0</v>
+      </c>
+      <c r="L11" s="35" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A12" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="B12" s="30">
+        <v>46238.5</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="D12" s="31">
+        <v>1</v>
+      </c>
+      <c r="E12" s="21">
+        <v>825</v>
+      </c>
+      <c r="F12" s="32">
+        <v>225</v>
+      </c>
+      <c r="G12" s="33">
+        <v>600</v>
+      </c>
+      <c r="H12" s="21">
+        <v>600</v>
+      </c>
+      <c r="I12" s="23">
+        <v>600</v>
+      </c>
+      <c r="J12" s="30">
+        <v>46266.5</v>
+      </c>
+      <c r="K12" s="34">
+        <v>0</v>
+      </c>
+      <c r="L12" s="35" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A13" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="B13" s="30">
+        <v>46238.5</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D13" s="31">
+        <v>1</v>
+      </c>
+      <c r="E13" s="21">
+        <v>825</v>
+      </c>
+      <c r="F13" s="32">
+        <v>825</v>
+      </c>
+      <c r="G13" s="33">
+        <v>0</v>
+      </c>
+      <c r="H13" s="21">
+        <v>0</v>
+      </c>
+      <c r="I13" s="34">
+        <v>0</v>
+      </c>
+      <c r="J13" s="30" t="s">
+        <v>77</v>
+      </c>
+      <c r="K13" s="34">
+        <v>0</v>
+      </c>
+      <c r="L13" s="35" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A14" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B14" s="30">
+        <v>46238.5</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D14" s="31">
+        <v>1</v>
+      </c>
+      <c r="E14" s="21">
+        <v>825</v>
+      </c>
+      <c r="F14" s="32">
+        <v>225</v>
+      </c>
+      <c r="G14" s="33">
+        <v>600</v>
+      </c>
+      <c r="H14" s="21">
+        <v>600</v>
+      </c>
+      <c r="I14" s="23">
+        <v>600</v>
+      </c>
+      <c r="J14" s="30">
+        <v>46261.5</v>
+      </c>
+      <c r="K14" s="34">
+        <v>0</v>
+      </c>
+      <c r="L14" s="35" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A15" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="B15" s="30">
+        <v>46239.5</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="D15" s="31">
+        <v>1</v>
+      </c>
+      <c r="E15" s="21">
+        <v>825</v>
+      </c>
+      <c r="F15" s="32">
+        <v>225</v>
+      </c>
+      <c r="G15" s="33">
+        <v>600</v>
+      </c>
+      <c r="H15" s="21">
+        <v>600</v>
+      </c>
+      <c r="I15" s="23">
+        <v>617.94</v>
+      </c>
+      <c r="J15" s="30">
+        <v>46252.5</v>
+      </c>
+      <c r="K15" s="34">
+        <v>0</v>
+      </c>
+      <c r="L15" s="35" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A16" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="B16" s="30">
+        <v>46239.5</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="D16" s="31">
+        <v>1</v>
+      </c>
+      <c r="E16" s="21">
+        <v>825</v>
+      </c>
+      <c r="F16" s="32">
+        <v>825</v>
+      </c>
+      <c r="G16" s="33">
+        <v>0</v>
+      </c>
+      <c r="H16" s="21">
+        <v>0</v>
+      </c>
+      <c r="I16" s="34">
+        <v>0</v>
+      </c>
+      <c r="J16" s="30" t="s">
+        <v>77</v>
+      </c>
+      <c r="K16" s="34">
+        <v>0</v>
+      </c>
+      <c r="L16" s="35" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A17" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="B17" s="30">
+        <v>46244.5</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="D17" s="31">
+        <v>1</v>
+      </c>
+      <c r="E17" s="21">
+        <v>825</v>
+      </c>
+      <c r="F17" s="32">
+        <v>825</v>
+      </c>
+      <c r="G17" s="33">
+        <v>0</v>
+      </c>
+      <c r="H17" s="21">
+        <v>0</v>
+      </c>
+      <c r="I17" s="34">
+        <v>0</v>
+      </c>
+      <c r="J17" s="30" t="s">
+        <v>77</v>
+      </c>
+      <c r="K17" s="34">
+        <v>0</v>
+      </c>
+      <c r="L17" s="35" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A18" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="B18" s="30">
+        <v>46244.5</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="D18" s="31">
+        <v>10</v>
+      </c>
+      <c r="E18" s="21">
+        <v>8250</v>
+      </c>
+      <c r="F18" s="32">
+        <v>2250</v>
+      </c>
+      <c r="G18" s="33">
+        <v>6000</v>
+      </c>
+      <c r="H18" s="21">
+        <v>6000</v>
+      </c>
+      <c r="I18" s="34">
+        <v>0</v>
+      </c>
+      <c r="J18" s="30" t="s">
+        <v>77</v>
+      </c>
+      <c r="K18" s="36">
+        <v>6000</v>
+      </c>
+      <c r="L18" s="35" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A19" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="B19" s="30">
+        <v>46244.5</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D19" s="31">
+        <v>2</v>
+      </c>
+      <c r="E19" s="21">
+        <v>1650</v>
+      </c>
+      <c r="F19" s="32">
+        <v>1650</v>
+      </c>
+      <c r="G19" s="33">
+        <v>0</v>
+      </c>
+      <c r="H19" s="21">
+        <v>0</v>
+      </c>
+      <c r="I19" s="34">
+        <v>0</v>
+      </c>
+      <c r="J19" s="30" t="s">
+        <v>77</v>
+      </c>
+      <c r="K19" s="34">
+        <v>0</v>
+      </c>
+      <c r="L19" s="35" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A20" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B20" s="30">
+        <v>46244.5</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D20" s="31">
+        <v>8</v>
+      </c>
+      <c r="E20" s="21">
+        <v>6600</v>
+      </c>
+      <c r="F20" s="32">
+        <v>1800</v>
+      </c>
+      <c r="G20" s="33">
+        <v>4800</v>
+      </c>
+      <c r="H20" s="21">
+        <v>4800</v>
+      </c>
+      <c r="I20" s="23">
+        <v>4800</v>
+      </c>
+      <c r="J20" s="30">
+        <v>46254.5</v>
+      </c>
+      <c r="K20" s="34">
+        <v>0</v>
+      </c>
+      <c r="L20" s="35" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A21" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="B21" s="30">
+        <v>46245.5</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D21" s="31">
+        <v>6</v>
+      </c>
+      <c r="E21" s="21">
+        <v>4950</v>
+      </c>
+      <c r="F21" s="32">
+        <v>4950</v>
+      </c>
+      <c r="G21" s="33">
+        <v>0</v>
+      </c>
+      <c r="H21" s="21">
+        <v>0</v>
+      </c>
+      <c r="I21" s="34">
+        <v>0</v>
+      </c>
+      <c r="J21" s="30" t="s">
+        <v>77</v>
+      </c>
+      <c r="K21" s="34">
+        <v>0</v>
+      </c>
+      <c r="L21" s="35" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A22" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B22" s="30">
+        <v>46245.5</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D22" s="31">
+        <v>16</v>
+      </c>
+      <c r="E22" s="21">
+        <v>13200</v>
+      </c>
+      <c r="F22" s="32">
+        <v>2700</v>
+      </c>
+      <c r="G22" s="33">
+        <v>10500</v>
+      </c>
+      <c r="H22" s="21">
+        <v>10500</v>
+      </c>
+      <c r="I22" s="23">
+        <v>10500</v>
+      </c>
+      <c r="J22" s="30">
+        <v>46262.5</v>
+      </c>
+      <c r="K22" s="34">
+        <v>0</v>
+      </c>
+      <c r="L22" s="35" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A23" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="B23" s="30">
+        <v>46245.5</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="D23" s="31">
+        <v>2</v>
+      </c>
+      <c r="E23" s="21">
+        <v>1650</v>
+      </c>
+      <c r="F23" s="32">
+        <v>1650</v>
+      </c>
+      <c r="G23" s="33">
+        <v>0</v>
+      </c>
+      <c r="H23" s="21">
+        <v>0</v>
+      </c>
+      <c r="I23" s="34">
+        <v>0</v>
+      </c>
+      <c r="J23" s="30" t="s">
+        <v>77</v>
+      </c>
+      <c r="K23" s="34">
+        <v>0</v>
+      </c>
+      <c r="L23" s="35" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A24" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B24" s="30">
+        <v>46245.5</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="D24" s="31">
+        <v>8</v>
+      </c>
+      <c r="E24" s="21">
+        <v>6600</v>
+      </c>
+      <c r="F24" s="32">
+        <v>1800</v>
+      </c>
+      <c r="G24" s="33">
+        <v>4800</v>
+      </c>
+      <c r="H24" s="21">
+        <v>4800</v>
+      </c>
+      <c r="I24" s="23">
+        <v>4800</v>
+      </c>
+      <c r="J24" s="30">
+        <v>46259.5</v>
+      </c>
+      <c r="K24" s="34">
+        <v>0</v>
+      </c>
+      <c r="L24" s="35" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A25" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="B25" s="30">
+        <v>46246.5</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="D25" s="31">
+        <v>2</v>
+      </c>
+      <c r="E25" s="21">
+        <v>1650</v>
+      </c>
+      <c r="F25" s="32">
+        <v>1650</v>
+      </c>
+      <c r="G25" s="33">
+        <v>0</v>
+      </c>
+      <c r="H25" s="21">
+        <v>0</v>
+      </c>
+      <c r="I25" s="34">
+        <v>0</v>
+      </c>
+      <c r="J25" s="30" t="s">
+        <v>77</v>
+      </c>
+      <c r="K25" s="34">
+        <v>0</v>
+      </c>
+      <c r="L25" s="35" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A26" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="B26" s="30">
+        <v>46246.5</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="D26" s="31">
+        <v>8</v>
+      </c>
+      <c r="E26" s="21">
+        <v>6600</v>
+      </c>
+      <c r="F26" s="32">
+        <v>1800</v>
+      </c>
+      <c r="G26" s="33">
+        <v>4800</v>
+      </c>
+      <c r="H26" s="21">
+        <v>4800</v>
+      </c>
+      <c r="I26" s="23">
+        <v>4943.52</v>
+      </c>
+      <c r="J26" s="30">
+        <v>46259.5</v>
+      </c>
+      <c r="K26" s="34">
+        <v>0</v>
+      </c>
+      <c r="L26" s="35" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A27" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="B27" s="30">
+        <v>46247.5</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="D27" s="31">
+        <v>3</v>
+      </c>
+      <c r="E27" s="21">
+        <v>2475</v>
+      </c>
+      <c r="F27" s="32">
+        <v>675</v>
+      </c>
+      <c r="G27" s="33">
+        <v>1800</v>
+      </c>
+      <c r="H27" s="21">
+        <v>1800</v>
+      </c>
+      <c r="I27" s="23">
+        <v>1800</v>
+      </c>
+      <c r="J27" s="30">
+        <v>46254.5</v>
+      </c>
+      <c r="K27" s="34">
+        <v>0</v>
+      </c>
+      <c r="L27" s="35" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A28" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="B28" s="30">
+        <v>46248.5</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="D28" s="31">
+        <v>2</v>
+      </c>
+      <c r="E28" s="21">
+        <v>1650</v>
+      </c>
+      <c r="F28" s="32">
+        <v>1650</v>
+      </c>
+      <c r="G28" s="33">
+        <v>0</v>
+      </c>
+      <c r="H28" s="21">
+        <v>0</v>
+      </c>
+      <c r="I28" s="34">
+        <v>0</v>
+      </c>
+      <c r="J28" s="30" t="s">
+        <v>77</v>
+      </c>
+      <c r="K28" s="34">
+        <v>0</v>
+      </c>
+      <c r="L28" s="35" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A29" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B29" s="30">
+        <v>46248.5</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="D29" s="31">
+        <v>8</v>
+      </c>
+      <c r="E29" s="21">
+        <v>6600</v>
+      </c>
+      <c r="F29" s="32">
+        <v>1800</v>
+      </c>
+      <c r="G29" s="33">
+        <v>4800</v>
+      </c>
+      <c r="H29" s="21">
+        <v>4800</v>
+      </c>
+      <c r="I29" s="23">
+        <v>4800</v>
+      </c>
+      <c r="J29" s="30">
+        <v>46254.5</v>
+      </c>
+      <c r="K29" s="34">
+        <v>0</v>
+      </c>
+      <c r="L29" s="35" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A30" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="B30" s="30">
+        <v>46253.5</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="D30" s="31">
+        <v>2</v>
+      </c>
+      <c r="E30" s="21">
+        <v>1650</v>
+      </c>
+      <c r="F30" s="32">
+        <v>1650</v>
+      </c>
+      <c r="G30" s="33">
+        <v>0</v>
+      </c>
+      <c r="H30" s="21">
+        <v>0</v>
+      </c>
+      <c r="I30" s="34">
+        <v>0</v>
+      </c>
+      <c r="J30" s="30" t="s">
+        <v>77</v>
+      </c>
+      <c r="K30" s="34">
+        <v>0</v>
+      </c>
+      <c r="L30" s="35" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A31" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="B31" s="30">
+        <v>46253.5</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="D31" s="31">
+        <v>8</v>
+      </c>
+      <c r="E31" s="21">
+        <v>6600</v>
+      </c>
+      <c r="F31" s="32">
+        <v>6600</v>
+      </c>
+      <c r="G31" s="33">
+        <v>0</v>
+      </c>
+      <c r="H31" s="21">
+        <v>0</v>
+      </c>
+      <c r="I31" s="34">
+        <v>0</v>
+      </c>
+      <c r="J31" s="30" t="s">
+        <v>77</v>
+      </c>
+      <c r="K31" s="34">
+        <v>0</v>
+      </c>
+      <c r="L31" s="35" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A32" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="B32" s="30">
+        <v>46254.5</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="D32" s="31">
+        <v>1</v>
+      </c>
+      <c r="E32" s="21">
+        <v>825</v>
+      </c>
+      <c r="F32" s="32">
+        <v>825</v>
+      </c>
+      <c r="G32" s="33">
+        <v>0</v>
+      </c>
+      <c r="H32" s="21">
+        <v>0</v>
+      </c>
+      <c r="I32" s="34">
+        <v>0</v>
+      </c>
+      <c r="J32" s="30" t="s">
+        <v>77</v>
+      </c>
+      <c r="K32" s="34">
+        <v>0</v>
+      </c>
+      <c r="L32" s="35" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A33" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="B33" s="30">
+        <v>46255.5</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="D33" s="31">
+        <v>2</v>
+      </c>
+      <c r="E33" s="21">
+        <v>1650</v>
+      </c>
+      <c r="F33" s="32">
+        <v>450</v>
+      </c>
+      <c r="G33" s="33">
+        <v>1200</v>
+      </c>
+      <c r="H33" s="21">
+        <v>1200</v>
+      </c>
+      <c r="I33" s="23">
+        <v>1200</v>
+      </c>
+      <c r="J33" s="30">
+        <v>46262.5</v>
+      </c>
+      <c r="K33" s="34">
+        <v>0</v>
+      </c>
+      <c r="L33" s="35" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A34" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="B34" s="30">
+        <v>46255.5</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="D34" s="31">
+        <v>4</v>
+      </c>
+      <c r="E34" s="21">
+        <v>3300</v>
+      </c>
+      <c r="F34" s="32">
+        <v>3300</v>
+      </c>
+      <c r="G34" s="33">
+        <v>0</v>
+      </c>
+      <c r="H34" s="21">
+        <v>0</v>
+      </c>
+      <c r="I34" s="34">
+        <v>0</v>
+      </c>
+      <c r="J34" s="30" t="s">
+        <v>77</v>
+      </c>
+      <c r="K34" s="34">
+        <v>0</v>
+      </c>
+      <c r="L34" s="35" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A35" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="B35" s="30">
+        <v>46255.5</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="D35" s="31">
+        <v>16</v>
+      </c>
+      <c r="E35" s="21">
+        <v>13200</v>
+      </c>
+      <c r="F35" s="32">
+        <v>3600</v>
+      </c>
+      <c r="G35" s="33">
+        <v>9600</v>
+      </c>
+      <c r="H35" s="21">
+        <v>9600</v>
+      </c>
+      <c r="I35" s="23">
+        <v>9600</v>
+      </c>
+      <c r="J35" s="30">
+        <v>46268.5</v>
+      </c>
+      <c r="K35" s="34">
+        <v>0</v>
+      </c>
+      <c r="L35" s="35" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A36" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="B36" s="30">
+        <v>46258.5</v>
+      </c>
+      <c r="C36" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="D36" s="31">
+        <v>2</v>
+      </c>
+      <c r="E36" s="21">
+        <v>1650</v>
+      </c>
+      <c r="F36" s="32">
+        <v>1650</v>
+      </c>
+      <c r="G36" s="33">
+        <v>0</v>
+      </c>
+      <c r="H36" s="21">
+        <v>0</v>
+      </c>
+      <c r="I36" s="34">
+        <v>0</v>
+      </c>
+      <c r="J36" s="30" t="s">
+        <v>77</v>
+      </c>
+      <c r="K36" s="34">
+        <v>0</v>
+      </c>
+      <c r="L36" s="35" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A37" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="B37" s="30">
+        <v>46258.5</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="D37" s="31">
+        <v>8</v>
+      </c>
+      <c r="E37" s="21">
+        <v>6600</v>
+      </c>
+      <c r="F37" s="32">
+        <v>1800</v>
+      </c>
+      <c r="G37" s="33">
+        <v>4800</v>
+      </c>
+      <c r="H37" s="21">
+        <v>4800</v>
+      </c>
+      <c r="I37" s="34">
+        <v>0</v>
+      </c>
+      <c r="J37" s="30" t="s">
+        <v>77</v>
+      </c>
+      <c r="K37" s="36">
+        <v>4800</v>
+      </c>
+      <c r="L37" s="35" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A38" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="B38" s="30">
+        <v>46259.5</v>
+      </c>
+      <c r="C38" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D38" s="31">
+        <v>5</v>
+      </c>
+      <c r="E38" s="21">
+        <v>4125</v>
+      </c>
+      <c r="F38" s="32">
+        <v>1125</v>
+      </c>
+      <c r="G38" s="33">
+        <v>3000</v>
+      </c>
+      <c r="H38" s="21">
+        <v>3000</v>
+      </c>
+      <c r="I38" s="34">
+        <v>0</v>
+      </c>
+      <c r="J38" s="30" t="s">
+        <v>77</v>
+      </c>
+      <c r="K38" s="36">
+        <v>3000</v>
+      </c>
+      <c r="L38" s="35" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A39" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="B39" s="30">
+        <v>46259.5</v>
+      </c>
+      <c r="C39" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="D39" s="31">
+        <v>1</v>
+      </c>
+      <c r="E39" s="21">
+        <v>825</v>
+      </c>
+      <c r="F39" s="32">
+        <v>825</v>
+      </c>
+      <c r="G39" s="33">
+        <v>0</v>
+      </c>
+      <c r="H39" s="21">
+        <v>0</v>
+      </c>
+      <c r="I39" s="34">
+        <v>0</v>
+      </c>
+      <c r="J39" s="30" t="s">
+        <v>77</v>
+      </c>
+      <c r="K39" s="34">
+        <v>0</v>
+      </c>
+      <c r="L39" s="35" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A40" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="B40" s="30">
+        <v>46259.5</v>
+      </c>
+      <c r="C40" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="D40" s="31">
+        <v>1</v>
+      </c>
+      <c r="E40" s="21">
+        <v>825</v>
+      </c>
+      <c r="F40" s="32">
+        <v>150</v>
+      </c>
+      <c r="G40" s="33">
+        <v>675</v>
+      </c>
+      <c r="H40" s="21">
+        <v>600</v>
+      </c>
+      <c r="I40" s="23">
+        <v>675</v>
+      </c>
+      <c r="J40" s="30">
+        <v>46266.5</v>
+      </c>
+      <c r="K40" s="34">
+        <v>0</v>
+      </c>
+      <c r="L40" s="35" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A41" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="B41" s="30">
+        <v>46261.5</v>
+      </c>
+      <c r="C41" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="D41" s="31">
+        <v>2</v>
+      </c>
+      <c r="E41" s="21">
+        <v>1650</v>
+      </c>
+      <c r="F41" s="32">
+        <v>450</v>
+      </c>
+      <c r="G41" s="33">
+        <v>1200</v>
+      </c>
+      <c r="H41" s="21">
+        <v>1200</v>
+      </c>
+      <c r="I41" s="34">
+        <v>0</v>
+      </c>
+      <c r="J41" s="30" t="s">
+        <v>77</v>
+      </c>
+      <c r="K41" s="36">
+        <v>1200</v>
+      </c>
+      <c r="L41" s="35" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A42" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="B42" s="30">
+        <v>46261.5</v>
+      </c>
+      <c r="C42" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="D42" s="31">
+        <v>1</v>
+      </c>
+      <c r="E42" s="21">
+        <v>825</v>
+      </c>
+      <c r="F42" s="32">
+        <v>225</v>
+      </c>
+      <c r="G42" s="33">
+        <v>600</v>
+      </c>
+      <c r="H42" s="21">
+        <v>600</v>
+      </c>
+      <c r="I42" s="34">
+        <v>0</v>
+      </c>
+      <c r="J42" s="30" t="s">
+        <v>77</v>
+      </c>
+      <c r="K42" s="36">
+        <v>600</v>
+      </c>
+      <c r="L42" s="35" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A43" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="B43" s="30">
+        <v>46261.5</v>
+      </c>
+      <c r="C43" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="D43" s="31">
+        <v>3</v>
+      </c>
+      <c r="E43" s="21">
+        <v>2475</v>
+      </c>
+      <c r="F43" s="32">
+        <v>2475</v>
+      </c>
+      <c r="G43" s="33">
+        <v>0</v>
+      </c>
+      <c r="H43" s="21">
+        <v>0</v>
+      </c>
+      <c r="I43" s="34">
+        <v>0</v>
+      </c>
+      <c r="J43" s="30" t="s">
+        <v>77</v>
+      </c>
+      <c r="K43" s="34">
+        <v>0</v>
+      </c>
+      <c r="L43" s="35" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A44" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="B44" s="30">
+        <v>46261.5</v>
+      </c>
+      <c r="C44" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="D44" s="31">
+        <v>7</v>
+      </c>
+      <c r="E44" s="21">
+        <v>5775</v>
+      </c>
+      <c r="F44" s="32">
+        <v>1575</v>
+      </c>
+      <c r="G44" s="33">
+        <v>4200</v>
+      </c>
+      <c r="H44" s="21">
+        <v>4200</v>
+      </c>
+      <c r="I44" s="23">
+        <v>4200</v>
+      </c>
+      <c r="J44" s="30">
+        <v>46280.5</v>
+      </c>
+      <c r="K44" s="34">
+        <v>0</v>
+      </c>
+      <c r="L44" s="35" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A45" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="B45" s="30">
+        <v>46265.5</v>
+      </c>
+      <c r="C45" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="D45" s="31">
+        <v>1</v>
+      </c>
+      <c r="E45" s="21">
+        <v>825</v>
+      </c>
+      <c r="F45" s="32">
+        <v>825</v>
+      </c>
+      <c r="G45" s="33">
+        <v>0</v>
+      </c>
+      <c r="H45" s="21">
+        <v>0</v>
+      </c>
+      <c r="I45" s="34">
+        <v>0</v>
+      </c>
+      <c r="J45" s="30" t="s">
+        <v>77</v>
+      </c>
+      <c r="K45" s="34">
+        <v>0</v>
+      </c>
+      <c r="L45" s="35" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A47" s="37" t="s">
+        <v>61</v>
+      </c>
+      <c r="C47" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="D47" s="38">
+        <v>172</v>
+      </c>
+      <c r="E47" s="33">
+        <v>141900</v>
+      </c>
+      <c r="F47" s="39">
+        <v>63525</v>
+      </c>
+      <c r="G47" s="40">
+        <v>78375</v>
+      </c>
+      <c r="H47" s="33">
+        <v>78300</v>
+      </c>
+      <c r="I47" s="41">
+        <v>62936.46000000001</v>
+      </c>
+      <c r="K47" s="42">
+        <v>15600</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
 </file>
--- a/commission/karin/2026-08.xlsx
+++ b/commission/karin/2026-08.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="125">
   <si>
     <t>Equine Performance Labs, LLC</t>
   </si>
@@ -26,7 +26,7 @@
     <t>Due By</t>
   </si>
   <si>
-    <t>September 30, 2026</t>
+    <t>2026-09-30</t>
   </si>
   <si>
     <t>August 2026 | Karin Williamson</t>
@@ -38,12 +38,6 @@
     <t>Q3 Route C Accelerator — tiered on invoiced revenue when $30K gate met (else standard waterfall)</t>
   </si>
   <si>
-    <t>Basis</t>
-  </si>
-  <si>
-    <t>✅ CRM + QuickBooks reconciled (paid on cleared)</t>
-  </si>
-  <si>
     <t>Route C — Q3 Accelerator</t>
   </si>
   <si>
@@ -56,34 +50,52 @@
     <t>New / Reactivated (15%)</t>
   </si>
   <si>
-    <t>on $21,900.00 collected</t>
+    <t>on $27,900.00 collected</t>
   </si>
   <si>
     <t>Growth above baseline (12.5%)</t>
   </si>
   <si>
-    <t>on $13,463.64 collected</t>
+    <t>on $11,400.00 collected</t>
   </si>
   <si>
     <t>Baseline reorders (10%)</t>
   </si>
   <si>
-    <t>on $8,736.36 collected</t>
+    <t>on $10,800.00 collected</t>
   </si>
   <si>
     <t>Spiff — 2 new acct(s) × $750</t>
   </si>
   <si>
-    <t>Breadth bonus — 8 accts ≥20%</t>
-  </si>
-  <si>
-    <t>Qualifying: Tanner Equine, Santa Lucia Farm, Signature Equine Hospital, Panorama Equine Medical and Surgical Center</t>
-  </si>
-  <si>
-    <t>vs. standard waterfall would have paid</t>
-  </si>
-  <si>
-    <t>Uplift: $6836.59</t>
+    <t>Earned on 2026-08 invoicing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">      • Republic of Texas Equine Medical Center (inv 2026-08-03, ORD-EPL-1161)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">      • David M Dutton, DVM PC (inv 2026-08-03, ORD-EPL-1159)</t>
+  </si>
+  <si>
+    <t>Breadth bonus — 6 accts ≥20% above baseline</t>
+  </si>
+  <si>
+    <t xml:space="preserve">      • Tanner Equine (11v vs baseline 4.3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">      • Equine Athlete Veterinary Services - Simpsonville, KY (20v vs baseline 7.3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">      • Santa Lucia Farm (10v vs baseline 2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">      • Smith Performance Equine (10v vs baseline 2.3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">      • Northern Star Equine (22v vs baseline 3.2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">      • Outlaw Equine (10v vs baseline 5.5)</t>
   </si>
   <si>
     <t>Account / Date</t>
@@ -419,11 +431,6 @@
     <font>
       <b/>
       <color rgb="0F5E4F"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="0F5E4F"/>
       <sz val="12"/>
     </font>
     <font>
@@ -452,6 +459,11 @@
     <font>
       <b/>
       <color rgb="FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="0F5E4F"/>
       <sz val="10"/>
     </font>
     <font>
@@ -535,7 +547,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -543,24 +555,22 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="10" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="13" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -583,7 +593,7 @@
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -607,7 +617,7 @@
     <xf numFmtId="164" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -962,7 +972,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H56"/>
+  <dimension ref="A1:H63"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
@@ -983,7 +993,7 @@
         <v>1</v>
       </c>
       <c r="H1" s="3">
-        <v>9341.59</v>
+        <v>10190</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
@@ -1008,590 +1018,684 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="7:8" x14ac:dyDescent="0.25">
-      <c r="G4" s="2" t="s">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" s="6" t="s">
         <v>8</v>
-      </c>
-      <c r="H4" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" s="7" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" s="8">
+        <v>9</v>
+      </c>
+      <c r="B6" s="7">
         <v>78375</v>
       </c>
-      <c r="C6" s="9" t="s">
-        <v>12</v>
+      <c r="C6" s="8" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7" s="10">
-        <v>3285</v>
-      </c>
-      <c r="C7" s="11" t="s">
-        <v>14</v>
+        <v>11</v>
+      </c>
+      <c r="B7" s="9">
+        <v>4185</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" s="10">
-        <v>1682.95</v>
-      </c>
-      <c r="C8" s="11" t="s">
-        <v>16</v>
+        <v>13</v>
+      </c>
+      <c r="B8" s="9">
+        <v>1425</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" s="9">
+        <v>1080</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B9" s="10">
-        <v>873.64</v>
-      </c>
-      <c r="C9" s="11" t="s">
+      <c r="B10" s="9">
+        <v>1500</v>
+      </c>
+      <c r="C10" s="10" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
+      <c r="D10" s="10"/>
+      <c r="E10" s="10"/>
+      <c r="F10" s="10"/>
+      <c r="G10" s="10"/>
+      <c r="H10" s="10"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="B10" s="10">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B11" s="10">
-        <v>2000</v>
-      </c>
-      <c r="C11" s="11" t="s">
-        <v>21</v>
-      </c>
+      <c r="B11" s="11"/>
+      <c r="C11" s="11"/>
       <c r="D11" s="11"/>
       <c r="E11" s="11"/>
       <c r="F11" s="11"/>
       <c r="G11" s="11"/>
       <c r="H11" s="11"/>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B12" s="11"/>
+      <c r="C12" s="11"/>
+      <c r="D12" s="11"/>
+      <c r="E12" s="11"/>
+      <c r="F12" s="11"/>
+      <c r="G12" s="11"/>
+      <c r="H12" s="11"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B13" s="9">
+        <v>2000</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="D13" s="10"/>
+      <c r="E13" s="10"/>
+      <c r="F13" s="10"/>
+      <c r="G13" s="10"/>
+      <c r="H13" s="10"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="B12" s="12">
-        <v>2505</v>
-      </c>
-      <c r="C12" s="13" t="s">
+      <c r="B14" s="11"/>
+      <c r="C14" s="11"/>
+      <c r="D14" s="11"/>
+      <c r="E14" s="11"/>
+      <c r="F14" s="11"/>
+      <c r="G14" s="11"/>
+      <c r="H14" s="11"/>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" s="11" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="14" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="14" t="s">
+      <c r="B15" s="11"/>
+      <c r="C15" s="11"/>
+      <c r="D15" s="11"/>
+      <c r="E15" s="11"/>
+      <c r="F15" s="11"/>
+      <c r="G15" s="11"/>
+      <c r="H15" s="11"/>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="B14" s="14" t="s">
+      <c r="B16" s="11"/>
+      <c r="C16" s="11"/>
+      <c r="D16" s="11"/>
+      <c r="E16" s="11"/>
+      <c r="F16" s="11"/>
+      <c r="G16" s="11"/>
+      <c r="H16" s="11"/>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="C14" s="14" t="s">
+      <c r="B17" s="11"/>
+      <c r="C17" s="11"/>
+      <c r="D17" s="11"/>
+      <c r="E17" s="11"/>
+      <c r="F17" s="11"/>
+      <c r="G17" s="11"/>
+      <c r="H17" s="11"/>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="D14" s="14" t="s">
+      <c r="B18" s="11"/>
+      <c r="C18" s="11"/>
+      <c r="D18" s="11"/>
+      <c r="E18" s="11"/>
+      <c r="F18" s="11"/>
+      <c r="G18" s="11"/>
+      <c r="H18" s="11"/>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="E14" s="14" t="s">
+      <c r="B19" s="11"/>
+      <c r="C19" s="11"/>
+      <c r="D19" s="11"/>
+      <c r="E19" s="11"/>
+      <c r="F19" s="11"/>
+      <c r="G19" s="11"/>
+      <c r="H19" s="11"/>
+    </row>
+    <row r="21" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="F14" s="15" t="s">
+      <c r="B21" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="G14" s="15" t="s">
+      <c r="C21" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="H14" s="15" t="s">
+      <c r="D21" s="12" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="16" t="s">
+      <c r="E21" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="F15" s="17">
+      <c r="F21" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="G21" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="H21" s="13" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="F22" s="15">
         <v>10500</v>
       </c>
-      <c r="H15" s="18">
+      <c r="H22" s="16">
         <v>1575</v>
       </c>
     </row>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B16" s="19">
+    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B23" s="17">
         <v>46262.5</v>
       </c>
-      <c r="C16" s="20" t="s">
-        <v>33</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="F16" s="21">
+      <c r="C23" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F23" s="19">
         <v>10500</v>
       </c>
-      <c r="G16" s="22">
+      <c r="G23" s="20">
         <v>0.15</v>
       </c>
-      <c r="H16" s="23">
+      <c r="H23" s="21">
         <v>1575</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="F18" s="17">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="F25" s="15">
         <v>7200</v>
       </c>
-      <c r="H18" s="18">
-        <v>829.09</v>
-      </c>
-    </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B19" s="19">
+      <c r="H25" s="16">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="26" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B26" s="17">
         <v>46254.5</v>
       </c>
-      <c r="C19" s="20" t="s">
-        <v>33</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="F19" s="21">
+      <c r="C26" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F26" s="19">
         <v>1800</v>
       </c>
-      <c r="G19" s="22">
-        <v>0.11515151515151516</v>
-      </c>
-      <c r="H19" s="23">
-        <v>207.27</v>
-      </c>
-    </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B20" s="19">
+      <c r="G26" s="20">
+        <v>0.1</v>
+      </c>
+      <c r="H26" s="21">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="27" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B27" s="17">
         <v>46254.5</v>
       </c>
-      <c r="C20" s="20" t="s">
-        <v>33</v>
-      </c>
-      <c r="E20" s="2" t="s">
+      <c r="C27" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="F20" s="21">
+      <c r="E27" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F27" s="19">
         <v>2400</v>
       </c>
-      <c r="G20" s="22">
-        <v>0.11515151515151516</v>
-      </c>
-      <c r="H20" s="23">
-        <v>276.36</v>
-      </c>
-    </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B21" s="19">
+      <c r="G27" s="20">
+        <v>0.1</v>
+      </c>
+      <c r="H27" s="21">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="28" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B28" s="17">
         <v>46261.5</v>
       </c>
-      <c r="C21" s="20" t="s">
-        <v>33</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F21" s="21">
+      <c r="C28" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F28" s="19">
         <v>600</v>
       </c>
-      <c r="G21" s="22">
-        <v>0.11515151515151516</v>
-      </c>
-      <c r="H21" s="23">
-        <v>69.09</v>
-      </c>
-    </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B22" s="19">
+      <c r="G28" s="20">
+        <v>0.1</v>
+      </c>
+      <c r="H28" s="21">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="29" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B29" s="17">
         <v>46261.5</v>
       </c>
-      <c r="C22" s="20" t="s">
-        <v>33</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="F22" s="21">
+      <c r="C29" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F29" s="19">
         <v>2400</v>
       </c>
-      <c r="G22" s="22">
-        <v>0.11515151515151516</v>
-      </c>
-      <c r="H22" s="23">
-        <v>276.36</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="16" t="s">
-        <v>40</v>
-      </c>
-      <c r="F24" s="17">
+      <c r="G29" s="20">
+        <v>0.1</v>
+      </c>
+      <c r="H29" s="21">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="F31" s="15">
         <v>4800</v>
       </c>
-      <c r="H24" s="18">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B25" s="19">
+      <c r="H31" s="16">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="32" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B32" s="17">
         <v>46239.5</v>
       </c>
-      <c r="C25" s="20" t="s">
-        <v>33</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="F25" s="21">
+      <c r="C32" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="F32" s="19">
         <v>4800</v>
       </c>
-      <c r="G25" s="22">
+      <c r="G32" s="20">
+        <v>0.15</v>
+      </c>
+      <c r="H32" s="21">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="F34" s="15">
+        <v>4800</v>
+      </c>
+      <c r="H34" s="16">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="35" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B35" s="17">
+        <v>46254.5</v>
+      </c>
+      <c r="C35" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="F35" s="19">
+        <v>4800</v>
+      </c>
+      <c r="G35" s="20">
+        <v>0.15</v>
+      </c>
+      <c r="H35" s="21">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="F37" s="15">
+        <v>4800</v>
+      </c>
+      <c r="H37" s="16">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="38" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B38" s="17">
+        <v>46254.5</v>
+      </c>
+      <c r="C38" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="F38" s="19">
+        <v>4800</v>
+      </c>
+      <c r="G38" s="20">
+        <v>0.125</v>
+      </c>
+      <c r="H38" s="21">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="F40" s="15">
+        <v>4800</v>
+      </c>
+      <c r="H40" s="16">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="41" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B41" s="17">
+        <v>46259.5</v>
+      </c>
+      <c r="C41" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F41" s="19">
+        <v>4800</v>
+      </c>
+      <c r="G41" s="20">
+        <v>0.15</v>
+      </c>
+      <c r="H41" s="21">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="F43" s="15">
+        <v>4800</v>
+      </c>
+      <c r="H43" s="16">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="44" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B44" s="17">
+        <v>46259.5</v>
+      </c>
+      <c r="C44" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="F44" s="19">
+        <v>4800</v>
+      </c>
+      <c r="G44" s="20">
+        <v>0.125</v>
+      </c>
+      <c r="H44" s="21">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="F46" s="15">
+        <v>3600</v>
+      </c>
+      <c r="H46" s="16">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="47" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B47" s="17">
+        <v>46254.5</v>
+      </c>
+      <c r="C47" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="F47" s="19">
+        <v>1800</v>
+      </c>
+      <c r="G47" s="20">
         <v>0.1</v>
       </c>
-      <c r="H25" s="23">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" s="16" t="s">
-        <v>42</v>
-      </c>
-      <c r="F27" s="17">
-        <v>4800</v>
-      </c>
-      <c r="H27" s="18">
-        <v>720</v>
-      </c>
-    </row>
-    <row r="28" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B28" s="19">
+      <c r="H47" s="21">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="48" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B48" s="17">
         <v>46254.5</v>
       </c>
-      <c r="C28" s="20" t="s">
-        <v>33</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F28" s="21">
-        <v>4800</v>
-      </c>
-      <c r="G28" s="22">
+      <c r="C48" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F48" s="19">
+        <v>1800</v>
+      </c>
+      <c r="G48" s="20">
+        <v>0.1</v>
+      </c>
+      <c r="H48" s="21">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="F50" s="15">
+        <v>1800</v>
+      </c>
+      <c r="H50" s="16">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="51" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B51" s="17">
+        <v>46259.5</v>
+      </c>
+      <c r="C51" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="F51" s="19">
+        <v>1800</v>
+      </c>
+      <c r="G51" s="20">
+        <v>0.125</v>
+      </c>
+      <c r="H51" s="21">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A53" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="F53" s="15">
+        <v>1200</v>
+      </c>
+      <c r="H53" s="16">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="54" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B54" s="17">
+        <v>46244.5</v>
+      </c>
+      <c r="C54" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="F54" s="19">
+        <v>1200</v>
+      </c>
+      <c r="G54" s="20">
         <v>0.15</v>
       </c>
-      <c r="H28" s="23">
-        <v>720</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" s="16" t="s">
-        <v>44</v>
-      </c>
-      <c r="F30" s="17">
-        <v>4800</v>
-      </c>
-      <c r="H30" s="18">
-        <v>576</v>
-      </c>
-    </row>
-    <row r="31" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B31" s="19">
-        <v>46254.5</v>
-      </c>
-      <c r="C31" s="20" t="s">
-        <v>33</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="F31" s="21">
-        <v>4800</v>
-      </c>
-      <c r="G31" s="22">
-        <v>0.12000000000000001</v>
-      </c>
-      <c r="H31" s="23">
-        <v>576</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A33" s="16" t="s">
-        <v>46</v>
-      </c>
-      <c r="F33" s="17">
-        <v>4800</v>
-      </c>
-      <c r="H33" s="18">
-        <v>720</v>
-      </c>
-    </row>
-    <row r="34" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B34" s="19">
-        <v>46259.5</v>
-      </c>
-      <c r="C34" s="20" t="s">
-        <v>33</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="F34" s="21">
-        <v>4800</v>
-      </c>
-      <c r="G34" s="22">
+      <c r="H54" s="21">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="F56" s="15">
+        <v>1200</v>
+      </c>
+      <c r="H56" s="16">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="57" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B57" s="17">
+        <v>46262.5</v>
+      </c>
+      <c r="C57" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="F57" s="19">
+        <v>1200</v>
+      </c>
+      <c r="G57" s="20">
         <v>0.15</v>
       </c>
-      <c r="H34" s="23">
-        <v>720</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A36" s="16" t="s">
-        <v>48</v>
-      </c>
-      <c r="F36" s="17">
-        <v>4800</v>
-      </c>
-      <c r="H36" s="18">
-        <v>584</v>
-      </c>
-    </row>
-    <row r="37" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B37" s="19">
-        <v>46259.5</v>
-      </c>
-      <c r="C37" s="20" t="s">
-        <v>33</v>
-      </c>
-      <c r="E37" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="F37" s="21">
-        <v>4800</v>
-      </c>
-      <c r="G37" s="22">
-        <v>0.12166666666666666</v>
-      </c>
-      <c r="H37" s="23">
-        <v>584</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A39" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="F39" s="17">
-        <v>3600</v>
-      </c>
-      <c r="H39" s="18">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="40" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B40" s="19">
-        <v>46254.5</v>
-      </c>
-      <c r="C40" s="20" t="s">
-        <v>33</v>
-      </c>
-      <c r="E40" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="F40" s="21">
-        <v>1800</v>
-      </c>
-      <c r="G40" s="22">
-        <v>0.1</v>
-      </c>
-      <c r="H40" s="23">
+      <c r="H57" s="21">
         <v>180</v>
       </c>
     </row>
-    <row r="41" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B41" s="19">
-        <v>46254.5</v>
-      </c>
-      <c r="C41" s="20" t="s">
-        <v>33</v>
-      </c>
-      <c r="E41" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="F41" s="21">
-        <v>1800</v>
-      </c>
-      <c r="G41" s="22">
-        <v>0.1</v>
-      </c>
-      <c r="H41" s="23">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A43" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="F43" s="17">
-        <v>1800</v>
-      </c>
-      <c r="H43" s="18">
-        <v>207.5</v>
-      </c>
-    </row>
-    <row r="44" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B44" s="19">
-        <v>46259.5</v>
-      </c>
-      <c r="C44" s="20" t="s">
-        <v>33</v>
-      </c>
-      <c r="E44" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="F44" s="21">
-        <v>1800</v>
-      </c>
-      <c r="G44" s="22">
-        <v>0.11527777777777777</v>
-      </c>
-      <c r="H44" s="23">
-        <v>207.5</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A46" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="F46" s="17">
-        <v>1200</v>
-      </c>
-      <c r="H46" s="18">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="47" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B47" s="19">
-        <v>46244.5</v>
-      </c>
-      <c r="C47" s="20" t="s">
-        <v>33</v>
-      </c>
-      <c r="E47" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="F47" s="21">
-        <v>1200</v>
-      </c>
-      <c r="G47" s="22">
-        <v>0.1</v>
-      </c>
-      <c r="H47" s="23">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A49" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="F49" s="17">
-        <v>1200</v>
-      </c>
-      <c r="H49" s="18">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="50" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B50" s="19">
-        <v>46262.5</v>
-      </c>
-      <c r="C50" s="20" t="s">
-        <v>33</v>
-      </c>
-      <c r="E50" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="F50" s="21">
-        <v>1200</v>
-      </c>
-      <c r="G50" s="22">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A59" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="F59" s="15">
+        <v>600</v>
+      </c>
+      <c r="H59" s="16">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="60" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B60" s="17">
+        <v>46252.5</v>
+      </c>
+      <c r="C60" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="F60" s="19">
+        <v>600</v>
+      </c>
+      <c r="G60" s="20">
         <v>0.15</v>
       </c>
-      <c r="H50" s="23">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A52" s="16" t="s">
-        <v>59</v>
-      </c>
-      <c r="F52" s="17">
-        <v>600</v>
-      </c>
-      <c r="H52" s="18">
+      <c r="H60" s="21">
         <v>90</v>
       </c>
     </row>
-    <row r="53" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B53" s="19">
-        <v>46252.5</v>
-      </c>
-      <c r="C53" s="20" t="s">
-        <v>33</v>
-      </c>
-      <c r="E53" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="F53" s="21">
-        <v>600</v>
-      </c>
-      <c r="G53" s="22">
-        <v>0.15</v>
-      </c>
-      <c r="H53" s="23">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A56" s="24" t="s">
-        <v>61</v>
-      </c>
-      <c r="F56" s="25">
-        <v>78375</v>
-      </c>
-      <c r="H56" s="26">
-        <v>9341.59</v>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A63" s="22" t="s">
+        <v>65</v>
+      </c>
+      <c r="F63" s="23">
+        <v>50100</v>
+      </c>
+      <c r="H63" s="24">
+        <v>10190</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="C11:H11"/>
+  <mergeCells count="10">
+    <mergeCell ref="C10:H10"/>
+    <mergeCell ref="A11:H11"/>
+    <mergeCell ref="A12:H12"/>
+    <mergeCell ref="C13:H13"/>
+    <mergeCell ref="A14:H14"/>
+    <mergeCell ref="A15:H15"/>
+    <mergeCell ref="A16:H16"/>
+    <mergeCell ref="A17:H17"/>
+    <mergeCell ref="A18:H18"/>
+    <mergeCell ref="A19:H19"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -1616,1605 +1720,1605 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="25" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" s="28" t="s">
-        <v>63</v>
+      <c r="A3" s="26" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" s="14" t="s">
-        <v>64</v>
-      </c>
-      <c r="B5" s="29" t="s">
-        <v>25</v>
-      </c>
-      <c r="C5" s="14" t="s">
-        <v>65</v>
-      </c>
-      <c r="D5" s="15" t="s">
-        <v>66</v>
-      </c>
-      <c r="E5" s="15" t="s">
-        <v>67</v>
-      </c>
-      <c r="F5" s="15" t="s">
+      <c r="A5" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="G5" s="15" t="s">
+      <c r="B5" s="27" t="s">
+        <v>29</v>
+      </c>
+      <c r="C5" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="H5" s="15" t="s">
+      <c r="D5" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="I5" s="15" t="s">
+      <c r="E5" s="13" t="s">
         <v>71</v>
       </c>
-      <c r="J5" s="29" t="s">
+      <c r="F5" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="K5" s="15" t="s">
+      <c r="G5" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="L5" s="29" t="s">
+      <c r="H5" s="13" t="s">
         <v>74</v>
+      </c>
+      <c r="I5" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="J5" s="27" t="s">
+        <v>76</v>
+      </c>
+      <c r="K5" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="L5" s="27" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="B6" s="30">
+        <v>79</v>
+      </c>
+      <c r="B6" s="28">
         <v>46237.5</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="D6" s="31">
+        <v>80</v>
+      </c>
+      <c r="D6" s="29">
         <v>2</v>
       </c>
-      <c r="E6" s="21">
+      <c r="E6" s="19">
         <v>1650</v>
       </c>
-      <c r="F6" s="32">
+      <c r="F6" s="30">
         <v>1650</v>
       </c>
-      <c r="G6" s="33">
-        <v>0</v>
-      </c>
-      <c r="H6" s="21">
-        <v>0</v>
-      </c>
-      <c r="I6" s="34">
-        <v>0</v>
-      </c>
-      <c r="J6" s="30" t="s">
-        <v>77</v>
-      </c>
-      <c r="K6" s="34">
-        <v>0</v>
-      </c>
-      <c r="L6" s="35" t="s">
-        <v>78</v>
+      <c r="G6" s="31">
+        <v>0</v>
+      </c>
+      <c r="H6" s="19">
+        <v>0</v>
+      </c>
+      <c r="I6" s="32">
+        <v>0</v>
+      </c>
+      <c r="J6" s="28" t="s">
+        <v>81</v>
+      </c>
+      <c r="K6" s="32">
+        <v>0</v>
+      </c>
+      <c r="L6" s="33" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="B7" s="30">
+        <v>83</v>
+      </c>
+      <c r="B7" s="28">
         <v>46237.5</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="D7" s="31">
+        <v>80</v>
+      </c>
+      <c r="D7" s="29">
         <v>8</v>
       </c>
-      <c r="E7" s="21">
+      <c r="E7" s="19">
         <v>6600</v>
       </c>
-      <c r="F7" s="32">
+      <c r="F7" s="30">
         <v>1800</v>
       </c>
-      <c r="G7" s="33">
+      <c r="G7" s="31">
         <v>4800</v>
       </c>
-      <c r="H7" s="21">
+      <c r="H7" s="19">
         <v>4800</v>
       </c>
-      <c r="I7" s="23">
+      <c r="I7" s="21">
         <v>4800</v>
       </c>
-      <c r="J7" s="30">
+      <c r="J7" s="28">
         <v>46275.5</v>
       </c>
-      <c r="K7" s="34">
-        <v>0</v>
-      </c>
-      <c r="L7" s="35" t="s">
-        <v>77</v>
+      <c r="K7" s="32">
+        <v>0</v>
+      </c>
+      <c r="L7" s="33" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="B8" s="30">
+        <v>84</v>
+      </c>
+      <c r="B8" s="28">
         <v>46237.5</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="D8" s="31">
+        <v>85</v>
+      </c>
+      <c r="D8" s="29">
         <v>2</v>
       </c>
-      <c r="E8" s="21">
+      <c r="E8" s="19">
         <v>1650</v>
       </c>
-      <c r="F8" s="32">
+      <c r="F8" s="30">
         <v>1650</v>
       </c>
-      <c r="G8" s="33">
-        <v>0</v>
-      </c>
-      <c r="H8" s="21">
-        <v>0</v>
-      </c>
-      <c r="I8" s="34">
-        <v>0</v>
-      </c>
-      <c r="J8" s="30" t="s">
-        <v>77</v>
-      </c>
-      <c r="K8" s="34">
-        <v>0</v>
-      </c>
-      <c r="L8" s="35" t="s">
-        <v>78</v>
+      <c r="G8" s="31">
+        <v>0</v>
+      </c>
+      <c r="H8" s="19">
+        <v>0</v>
+      </c>
+      <c r="I8" s="32">
+        <v>0</v>
+      </c>
+      <c r="J8" s="28" t="s">
+        <v>81</v>
+      </c>
+      <c r="K8" s="32">
+        <v>0</v>
+      </c>
+      <c r="L8" s="33" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="B9" s="30">
+        <v>86</v>
+      </c>
+      <c r="B9" s="28">
         <v>46237.5</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="D9" s="31">
+        <v>85</v>
+      </c>
+      <c r="D9" s="29">
         <v>8</v>
       </c>
-      <c r="E9" s="21">
+      <c r="E9" s="19">
         <v>6600</v>
       </c>
-      <c r="F9" s="32">
+      <c r="F9" s="30">
         <v>1800</v>
       </c>
-      <c r="G9" s="33">
+      <c r="G9" s="31">
         <v>4800</v>
       </c>
-      <c r="H9" s="21">
+      <c r="H9" s="19">
         <v>4800</v>
       </c>
-      <c r="I9" s="23">
+      <c r="I9" s="21">
         <v>4800</v>
       </c>
-      <c r="J9" s="30">
+      <c r="J9" s="28">
         <v>46274.5</v>
       </c>
-      <c r="K9" s="34">
-        <v>0</v>
-      </c>
-      <c r="L9" s="35" t="s">
-        <v>77</v>
+      <c r="K9" s="32">
+        <v>0</v>
+      </c>
+      <c r="L9" s="33" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B10" s="28">
+        <v>46237.5</v>
+      </c>
+      <c r="C10" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B10" s="30">
-        <v>46237.5</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="D10" s="31">
+      <c r="D10" s="29">
         <v>4</v>
       </c>
-      <c r="E10" s="21">
+      <c r="E10" s="19">
         <v>3300</v>
       </c>
-      <c r="F10" s="32">
+      <c r="F10" s="30">
         <v>900</v>
       </c>
-      <c r="G10" s="33">
+      <c r="G10" s="31">
         <v>2400</v>
       </c>
-      <c r="H10" s="21">
+      <c r="H10" s="19">
         <v>2400</v>
       </c>
-      <c r="I10" s="23">
+      <c r="I10" s="21">
         <v>2400</v>
       </c>
-      <c r="J10" s="30">
+      <c r="J10" s="28">
         <v>46261.5</v>
       </c>
-      <c r="K10" s="34">
-        <v>0</v>
-      </c>
-      <c r="L10" s="35" t="s">
-        <v>77</v>
+      <c r="K10" s="32">
+        <v>0</v>
+      </c>
+      <c r="L10" s="33" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="B11" s="30">
+        <v>58</v>
+      </c>
+      <c r="B11" s="28">
         <v>46237.5</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="D11" s="31">
+        <v>57</v>
+      </c>
+      <c r="D11" s="29">
         <v>3</v>
       </c>
-      <c r="E11" s="21">
+      <c r="E11" s="19">
         <v>2475</v>
       </c>
-      <c r="F11" s="32">
+      <c r="F11" s="30">
         <v>675</v>
       </c>
-      <c r="G11" s="33">
+      <c r="G11" s="31">
         <v>1800</v>
       </c>
-      <c r="H11" s="21">
+      <c r="H11" s="19">
         <v>1800</v>
       </c>
-      <c r="I11" s="23">
+      <c r="I11" s="21">
         <v>1800</v>
       </c>
-      <c r="J11" s="30">
+      <c r="J11" s="28">
         <v>46259.5</v>
       </c>
-      <c r="K11" s="34">
-        <v>0</v>
-      </c>
-      <c r="L11" s="35" t="s">
-        <v>77</v>
+      <c r="K11" s="32">
+        <v>0</v>
+      </c>
+      <c r="L11" s="33" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="B12" s="30">
+        <v>87</v>
+      </c>
+      <c r="B12" s="28">
         <v>46238.5</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="D12" s="31">
+        <v>88</v>
+      </c>
+      <c r="D12" s="29">
         <v>1</v>
       </c>
-      <c r="E12" s="21">
+      <c r="E12" s="19">
         <v>825</v>
       </c>
-      <c r="F12" s="32">
+      <c r="F12" s="30">
         <v>225</v>
       </c>
-      <c r="G12" s="33">
+      <c r="G12" s="31">
         <v>600</v>
       </c>
-      <c r="H12" s="21">
+      <c r="H12" s="19">
         <v>600</v>
       </c>
-      <c r="I12" s="23">
+      <c r="I12" s="21">
         <v>600</v>
       </c>
-      <c r="J12" s="30">
+      <c r="J12" s="28">
         <v>46266.5</v>
       </c>
-      <c r="K12" s="34">
-        <v>0</v>
-      </c>
-      <c r="L12" s="35" t="s">
-        <v>77</v>
+      <c r="K12" s="32">
+        <v>0</v>
+      </c>
+      <c r="L12" s="33" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="B13" s="30">
+        <v>89</v>
+      </c>
+      <c r="B13" s="28">
         <v>46238.5</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="D13" s="31">
+        <v>39</v>
+      </c>
+      <c r="D13" s="29">
         <v>1</v>
       </c>
-      <c r="E13" s="21">
+      <c r="E13" s="19">
         <v>825</v>
       </c>
-      <c r="F13" s="32">
+      <c r="F13" s="30">
         <v>825</v>
       </c>
-      <c r="G13" s="33">
-        <v>0</v>
-      </c>
-      <c r="H13" s="21">
-        <v>0</v>
-      </c>
-      <c r="I13" s="34">
-        <v>0</v>
-      </c>
-      <c r="J13" s="30" t="s">
-        <v>77</v>
-      </c>
-      <c r="K13" s="34">
-        <v>0</v>
-      </c>
-      <c r="L13" s="35" t="s">
-        <v>86</v>
+      <c r="G13" s="31">
+        <v>0</v>
+      </c>
+      <c r="H13" s="19">
+        <v>0</v>
+      </c>
+      <c r="I13" s="32">
+        <v>0</v>
+      </c>
+      <c r="J13" s="28" t="s">
+        <v>81</v>
+      </c>
+      <c r="K13" s="32">
+        <v>0</v>
+      </c>
+      <c r="L13" s="33" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B14" s="30">
+        <v>42</v>
+      </c>
+      <c r="B14" s="28">
         <v>46238.5</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="D14" s="31">
+        <v>39</v>
+      </c>
+      <c r="D14" s="29">
         <v>1</v>
       </c>
-      <c r="E14" s="21">
+      <c r="E14" s="19">
         <v>825</v>
       </c>
-      <c r="F14" s="32">
+      <c r="F14" s="30">
         <v>225</v>
       </c>
-      <c r="G14" s="33">
+      <c r="G14" s="31">
         <v>600</v>
       </c>
-      <c r="H14" s="21">
+      <c r="H14" s="19">
         <v>600</v>
       </c>
-      <c r="I14" s="23">
+      <c r="I14" s="21">
         <v>600</v>
       </c>
-      <c r="J14" s="30">
+      <c r="J14" s="28">
         <v>46261.5</v>
       </c>
-      <c r="K14" s="34">
-        <v>0</v>
-      </c>
-      <c r="L14" s="35" t="s">
-        <v>77</v>
+      <c r="K14" s="32">
+        <v>0</v>
+      </c>
+      <c r="L14" s="33" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="B15" s="30">
+        <v>64</v>
+      </c>
+      <c r="B15" s="28">
         <v>46239.5</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="D15" s="31">
+        <v>63</v>
+      </c>
+      <c r="D15" s="29">
         <v>1</v>
       </c>
-      <c r="E15" s="21">
+      <c r="E15" s="19">
         <v>825</v>
       </c>
-      <c r="F15" s="32">
+      <c r="F15" s="30">
         <v>225</v>
       </c>
-      <c r="G15" s="33">
+      <c r="G15" s="31">
         <v>600</v>
       </c>
-      <c r="H15" s="21">
+      <c r="H15" s="19">
         <v>600</v>
       </c>
-      <c r="I15" s="23">
+      <c r="I15" s="21">
         <v>617.94</v>
       </c>
-      <c r="J15" s="30">
+      <c r="J15" s="28">
         <v>46252.5</v>
       </c>
-      <c r="K15" s="34">
-        <v>0</v>
-      </c>
-      <c r="L15" s="35" t="s">
-        <v>77</v>
+      <c r="K15" s="32">
+        <v>0</v>
+      </c>
+      <c r="L15" s="33" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="B16" s="30">
+        <v>91</v>
+      </c>
+      <c r="B16" s="28">
         <v>46239.5</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="D16" s="31">
+        <v>92</v>
+      </c>
+      <c r="D16" s="29">
         <v>1</v>
       </c>
-      <c r="E16" s="21">
+      <c r="E16" s="19">
         <v>825</v>
       </c>
-      <c r="F16" s="32">
+      <c r="F16" s="30">
         <v>825</v>
       </c>
-      <c r="G16" s="33">
-        <v>0</v>
-      </c>
-      <c r="H16" s="21">
-        <v>0</v>
-      </c>
-      <c r="I16" s="34">
-        <v>0</v>
-      </c>
-      <c r="J16" s="30" t="s">
-        <v>77</v>
-      </c>
-      <c r="K16" s="34">
-        <v>0</v>
-      </c>
-      <c r="L16" s="35" t="s">
-        <v>86</v>
+      <c r="G16" s="31">
+        <v>0</v>
+      </c>
+      <c r="H16" s="19">
+        <v>0</v>
+      </c>
+      <c r="I16" s="32">
+        <v>0</v>
+      </c>
+      <c r="J16" s="28" t="s">
+        <v>81</v>
+      </c>
+      <c r="K16" s="32">
+        <v>0</v>
+      </c>
+      <c r="L16" s="33" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="B17" s="30">
+        <v>93</v>
+      </c>
+      <c r="B17" s="28">
         <v>46244.5</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="D17" s="31">
+        <v>92</v>
+      </c>
+      <c r="D17" s="29">
         <v>1</v>
       </c>
-      <c r="E17" s="21">
+      <c r="E17" s="19">
         <v>825</v>
       </c>
-      <c r="F17" s="32">
+      <c r="F17" s="30">
         <v>825</v>
       </c>
-      <c r="G17" s="33">
-        <v>0</v>
-      </c>
-      <c r="H17" s="21">
-        <v>0</v>
-      </c>
-      <c r="I17" s="34">
-        <v>0</v>
-      </c>
-      <c r="J17" s="30" t="s">
-        <v>77</v>
-      </c>
-      <c r="K17" s="34">
-        <v>0</v>
-      </c>
-      <c r="L17" s="35" t="s">
-        <v>86</v>
+      <c r="G17" s="31">
+        <v>0</v>
+      </c>
+      <c r="H17" s="19">
+        <v>0</v>
+      </c>
+      <c r="I17" s="32">
+        <v>0</v>
+      </c>
+      <c r="J17" s="28" t="s">
+        <v>81</v>
+      </c>
+      <c r="K17" s="32">
+        <v>0</v>
+      </c>
+      <c r="L17" s="33" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="B18" s="30">
+        <v>94</v>
+      </c>
+      <c r="B18" s="28">
         <v>46244.5</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="D18" s="31">
+        <v>95</v>
+      </c>
+      <c r="D18" s="29">
         <v>10</v>
       </c>
-      <c r="E18" s="21">
+      <c r="E18" s="19">
         <v>8250</v>
       </c>
-      <c r="F18" s="32">
+      <c r="F18" s="30">
         <v>2250</v>
       </c>
-      <c r="G18" s="33">
+      <c r="G18" s="31">
         <v>6000</v>
       </c>
-      <c r="H18" s="21">
+      <c r="H18" s="19">
         <v>6000</v>
       </c>
-      <c r="I18" s="34">
-        <v>0</v>
-      </c>
-      <c r="J18" s="30" t="s">
-        <v>77</v>
-      </c>
-      <c r="K18" s="36">
+      <c r="I18" s="21">
         <v>6000</v>
       </c>
-      <c r="L18" s="35" t="s">
-        <v>77</v>
+      <c r="J18" s="28">
+        <v>46296.5</v>
+      </c>
+      <c r="K18" s="32">
+        <v>0</v>
+      </c>
+      <c r="L18" s="33" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="B19" s="30">
+        <v>96</v>
+      </c>
+      <c r="B19" s="28">
         <v>46244.5</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="D19" s="31">
+        <v>46</v>
+      </c>
+      <c r="D19" s="29">
         <v>2</v>
       </c>
-      <c r="E19" s="21">
+      <c r="E19" s="19">
         <v>1650</v>
       </c>
-      <c r="F19" s="32">
+      <c r="F19" s="30">
         <v>1650</v>
       </c>
-      <c r="G19" s="33">
-        <v>0</v>
-      </c>
-      <c r="H19" s="21">
-        <v>0</v>
-      </c>
-      <c r="I19" s="34">
-        <v>0</v>
-      </c>
-      <c r="J19" s="30" t="s">
-        <v>77</v>
-      </c>
-      <c r="K19" s="34">
-        <v>0</v>
-      </c>
-      <c r="L19" s="35" t="s">
-        <v>78</v>
+      <c r="G19" s="31">
+        <v>0</v>
+      </c>
+      <c r="H19" s="19">
+        <v>0</v>
+      </c>
+      <c r="I19" s="32">
+        <v>0</v>
+      </c>
+      <c r="J19" s="28" t="s">
+        <v>81</v>
+      </c>
+      <c r="K19" s="32">
+        <v>0</v>
+      </c>
+      <c r="L19" s="33" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B20" s="30">
+        <v>47</v>
+      </c>
+      <c r="B20" s="28">
         <v>46244.5</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="D20" s="31">
+        <v>46</v>
+      </c>
+      <c r="D20" s="29">
         <v>8</v>
       </c>
-      <c r="E20" s="21">
+      <c r="E20" s="19">
         <v>6600</v>
       </c>
-      <c r="F20" s="32">
+      <c r="F20" s="30">
         <v>1800</v>
       </c>
-      <c r="G20" s="33">
+      <c r="G20" s="31">
         <v>4800</v>
       </c>
-      <c r="H20" s="21">
+      <c r="H20" s="19">
         <v>4800</v>
       </c>
-      <c r="I20" s="23">
+      <c r="I20" s="21">
         <v>4800</v>
       </c>
-      <c r="J20" s="30">
+      <c r="J20" s="28">
         <v>46254.5</v>
       </c>
-      <c r="K20" s="34">
-        <v>0</v>
-      </c>
-      <c r="L20" s="35" t="s">
-        <v>77</v>
+      <c r="K20" s="32">
+        <v>0</v>
+      </c>
+      <c r="L20" s="33" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="B21" s="30">
+        <v>97</v>
+      </c>
+      <c r="B21" s="28">
         <v>46245.5</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="D21" s="31">
+        <v>36</v>
+      </c>
+      <c r="D21" s="29">
         <v>6</v>
       </c>
-      <c r="E21" s="21">
+      <c r="E21" s="19">
         <v>4950</v>
       </c>
-      <c r="F21" s="32">
+      <c r="F21" s="30">
         <v>4950</v>
       </c>
-      <c r="G21" s="33">
-        <v>0</v>
-      </c>
-      <c r="H21" s="21">
-        <v>0</v>
-      </c>
-      <c r="I21" s="34">
-        <v>0</v>
-      </c>
-      <c r="J21" s="30" t="s">
-        <v>77</v>
-      </c>
-      <c r="K21" s="34">
-        <v>0</v>
-      </c>
-      <c r="L21" s="35" t="s">
-        <v>78</v>
+      <c r="G21" s="31">
+        <v>0</v>
+      </c>
+      <c r="H21" s="19">
+        <v>0</v>
+      </c>
+      <c r="I21" s="32">
+        <v>0</v>
+      </c>
+      <c r="J21" s="28" t="s">
+        <v>81</v>
+      </c>
+      <c r="K21" s="32">
+        <v>0</v>
+      </c>
+      <c r="L21" s="33" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="B22" s="30">
+        <v>38</v>
+      </c>
+      <c r="B22" s="28">
         <v>46245.5</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="D22" s="31">
+        <v>36</v>
+      </c>
+      <c r="D22" s="29">
         <v>16</v>
       </c>
-      <c r="E22" s="21">
+      <c r="E22" s="19">
         <v>13200</v>
       </c>
-      <c r="F22" s="32">
+      <c r="F22" s="30">
         <v>2700</v>
       </c>
-      <c r="G22" s="33">
+      <c r="G22" s="31">
         <v>10500</v>
       </c>
-      <c r="H22" s="21">
+      <c r="H22" s="19">
         <v>10500</v>
       </c>
-      <c r="I22" s="23">
+      <c r="I22" s="21">
         <v>10500</v>
       </c>
-      <c r="J22" s="30">
+      <c r="J22" s="28">
         <v>46262.5</v>
       </c>
-      <c r="K22" s="34">
-        <v>0</v>
-      </c>
-      <c r="L22" s="35" t="s">
-        <v>77</v>
+      <c r="K22" s="32">
+        <v>0</v>
+      </c>
+      <c r="L22" s="33" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="B23" s="30">
+        <v>98</v>
+      </c>
+      <c r="B23" s="28">
         <v>46245.5</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="D23" s="31">
+        <v>52</v>
+      </c>
+      <c r="D23" s="29">
         <v>2</v>
       </c>
-      <c r="E23" s="21">
+      <c r="E23" s="19">
         <v>1650</v>
       </c>
-      <c r="F23" s="32">
+      <c r="F23" s="30">
         <v>1650</v>
       </c>
-      <c r="G23" s="33">
-        <v>0</v>
-      </c>
-      <c r="H23" s="21">
-        <v>0</v>
-      </c>
-      <c r="I23" s="34">
-        <v>0</v>
-      </c>
-      <c r="J23" s="30" t="s">
-        <v>77</v>
-      </c>
-      <c r="K23" s="34">
-        <v>0</v>
-      </c>
-      <c r="L23" s="35" t="s">
-        <v>78</v>
+      <c r="G23" s="31">
+        <v>0</v>
+      </c>
+      <c r="H23" s="19">
+        <v>0</v>
+      </c>
+      <c r="I23" s="32">
+        <v>0</v>
+      </c>
+      <c r="J23" s="28" t="s">
+        <v>81</v>
+      </c>
+      <c r="K23" s="32">
+        <v>0</v>
+      </c>
+      <c r="L23" s="33" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="B24" s="30">
+        <v>53</v>
+      </c>
+      <c r="B24" s="28">
         <v>46245.5</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="D24" s="31">
+        <v>52</v>
+      </c>
+      <c r="D24" s="29">
         <v>8</v>
       </c>
-      <c r="E24" s="21">
+      <c r="E24" s="19">
         <v>6600</v>
       </c>
-      <c r="F24" s="32">
+      <c r="F24" s="30">
         <v>1800</v>
       </c>
-      <c r="G24" s="33">
+      <c r="G24" s="31">
         <v>4800</v>
       </c>
-      <c r="H24" s="21">
+      <c r="H24" s="19">
         <v>4800</v>
       </c>
-      <c r="I24" s="23">
+      <c r="I24" s="21">
         <v>4800</v>
       </c>
-      <c r="J24" s="30">
+      <c r="J24" s="28">
         <v>46259.5</v>
       </c>
-      <c r="K24" s="34">
-        <v>0</v>
-      </c>
-      <c r="L24" s="35" t="s">
-        <v>77</v>
+      <c r="K24" s="32">
+        <v>0</v>
+      </c>
+      <c r="L24" s="33" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="B25" s="30">
+        <v>99</v>
+      </c>
+      <c r="B25" s="28">
         <v>46246.5</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="D25" s="31">
+        <v>50</v>
+      </c>
+      <c r="D25" s="29">
         <v>2</v>
       </c>
-      <c r="E25" s="21">
+      <c r="E25" s="19">
         <v>1650</v>
       </c>
-      <c r="F25" s="32">
+      <c r="F25" s="30">
         <v>1650</v>
       </c>
-      <c r="G25" s="33">
-        <v>0</v>
-      </c>
-      <c r="H25" s="21">
-        <v>0</v>
-      </c>
-      <c r="I25" s="34">
-        <v>0</v>
-      </c>
-      <c r="J25" s="30" t="s">
-        <v>77</v>
-      </c>
-      <c r="K25" s="34">
-        <v>0</v>
-      </c>
-      <c r="L25" s="35" t="s">
-        <v>78</v>
+      <c r="G25" s="31">
+        <v>0</v>
+      </c>
+      <c r="H25" s="19">
+        <v>0</v>
+      </c>
+      <c r="I25" s="32">
+        <v>0</v>
+      </c>
+      <c r="J25" s="28" t="s">
+        <v>81</v>
+      </c>
+      <c r="K25" s="32">
+        <v>0</v>
+      </c>
+      <c r="L25" s="33" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="B26" s="30">
+        <v>51</v>
+      </c>
+      <c r="B26" s="28">
         <v>46246.5</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="D26" s="31">
+        <v>50</v>
+      </c>
+      <c r="D26" s="29">
         <v>8</v>
       </c>
-      <c r="E26" s="21">
+      <c r="E26" s="19">
         <v>6600</v>
       </c>
-      <c r="F26" s="32">
+      <c r="F26" s="30">
         <v>1800</v>
       </c>
-      <c r="G26" s="33">
+      <c r="G26" s="31">
         <v>4800</v>
       </c>
-      <c r="H26" s="21">
+      <c r="H26" s="19">
         <v>4800</v>
       </c>
-      <c r="I26" s="23">
+      <c r="I26" s="21">
         <v>4943.52</v>
       </c>
-      <c r="J26" s="30">
+      <c r="J26" s="28">
         <v>46259.5</v>
       </c>
-      <c r="K26" s="34">
-        <v>0</v>
-      </c>
-      <c r="L26" s="35" t="s">
-        <v>77</v>
+      <c r="K26" s="32">
+        <v>0</v>
+      </c>
+      <c r="L26" s="33" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="B27" s="30">
+        <v>55</v>
+      </c>
+      <c r="B27" s="28">
         <v>46247.5</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="D27" s="31">
+        <v>54</v>
+      </c>
+      <c r="D27" s="29">
         <v>3</v>
       </c>
-      <c r="E27" s="21">
+      <c r="E27" s="19">
         <v>2475</v>
       </c>
-      <c r="F27" s="32">
+      <c r="F27" s="30">
         <v>675</v>
       </c>
-      <c r="G27" s="33">
+      <c r="G27" s="31">
         <v>1800</v>
       </c>
-      <c r="H27" s="21">
+      <c r="H27" s="19">
         <v>1800</v>
       </c>
-      <c r="I27" s="23">
+      <c r="I27" s="21">
         <v>1800</v>
       </c>
-      <c r="J27" s="30">
+      <c r="J27" s="28">
         <v>46254.5</v>
       </c>
-      <c r="K27" s="34">
-        <v>0</v>
-      </c>
-      <c r="L27" s="35" t="s">
-        <v>77</v>
+      <c r="K27" s="32">
+        <v>0</v>
+      </c>
+      <c r="L27" s="33" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="B28" s="30">
+        <v>100</v>
+      </c>
+      <c r="B28" s="28">
         <v>46248.5</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="D28" s="31">
+        <v>48</v>
+      </c>
+      <c r="D28" s="29">
         <v>2</v>
       </c>
-      <c r="E28" s="21">
+      <c r="E28" s="19">
         <v>1650</v>
       </c>
-      <c r="F28" s="32">
+      <c r="F28" s="30">
         <v>1650</v>
       </c>
-      <c r="G28" s="33">
-        <v>0</v>
-      </c>
-      <c r="H28" s="21">
-        <v>0</v>
-      </c>
-      <c r="I28" s="34">
-        <v>0</v>
-      </c>
-      <c r="J28" s="30" t="s">
-        <v>77</v>
-      </c>
-      <c r="K28" s="34">
-        <v>0</v>
-      </c>
-      <c r="L28" s="35" t="s">
-        <v>86</v>
+      <c r="G28" s="31">
+        <v>0</v>
+      </c>
+      <c r="H28" s="19">
+        <v>0</v>
+      </c>
+      <c r="I28" s="32">
+        <v>0</v>
+      </c>
+      <c r="J28" s="28" t="s">
+        <v>81</v>
+      </c>
+      <c r="K28" s="32">
+        <v>0</v>
+      </c>
+      <c r="L28" s="33" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B29" s="30">
+        <v>49</v>
+      </c>
+      <c r="B29" s="28">
         <v>46248.5</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="D29" s="31">
+        <v>48</v>
+      </c>
+      <c r="D29" s="29">
         <v>8</v>
       </c>
-      <c r="E29" s="21">
+      <c r="E29" s="19">
         <v>6600</v>
       </c>
-      <c r="F29" s="32">
+      <c r="F29" s="30">
         <v>1800</v>
       </c>
-      <c r="G29" s="33">
+      <c r="G29" s="31">
         <v>4800</v>
       </c>
-      <c r="H29" s="21">
+      <c r="H29" s="19">
         <v>4800</v>
       </c>
-      <c r="I29" s="23">
+      <c r="I29" s="21">
         <v>4800</v>
       </c>
-      <c r="J29" s="30">
+      <c r="J29" s="28">
         <v>46254.5</v>
       </c>
-      <c r="K29" s="34">
-        <v>0</v>
-      </c>
-      <c r="L29" s="35" t="s">
-        <v>77</v>
+      <c r="K29" s="32">
+        <v>0</v>
+      </c>
+      <c r="L29" s="33" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="B30" s="30">
+        <v>101</v>
+      </c>
+      <c r="B30" s="28">
         <v>46253.5</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="D30" s="31">
+        <v>102</v>
+      </c>
+      <c r="D30" s="29">
         <v>2</v>
       </c>
-      <c r="E30" s="21">
+      <c r="E30" s="19">
         <v>1650</v>
       </c>
-      <c r="F30" s="32">
+      <c r="F30" s="30">
         <v>1650</v>
       </c>
-      <c r="G30" s="33">
-        <v>0</v>
-      </c>
-      <c r="H30" s="21">
-        <v>0</v>
-      </c>
-      <c r="I30" s="34">
-        <v>0</v>
-      </c>
-      <c r="J30" s="30" t="s">
-        <v>77</v>
-      </c>
-      <c r="K30" s="34">
-        <v>0</v>
-      </c>
-      <c r="L30" s="35" t="s">
-        <v>78</v>
+      <c r="G30" s="31">
+        <v>0</v>
+      </c>
+      <c r="H30" s="19">
+        <v>0</v>
+      </c>
+      <c r="I30" s="32">
+        <v>0</v>
+      </c>
+      <c r="J30" s="28" t="s">
+        <v>81</v>
+      </c>
+      <c r="K30" s="32">
+        <v>0</v>
+      </c>
+      <c r="L30" s="33" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="B31" s="30">
+        <v>103</v>
+      </c>
+      <c r="B31" s="28">
         <v>46253.5</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="D31" s="31">
+        <v>102</v>
+      </c>
+      <c r="D31" s="29">
         <v>8</v>
       </c>
-      <c r="E31" s="21">
+      <c r="E31" s="19">
         <v>6600</v>
       </c>
-      <c r="F31" s="32">
+      <c r="F31" s="30">
         <v>6600</v>
       </c>
-      <c r="G31" s="33">
-        <v>0</v>
-      </c>
-      <c r="H31" s="21">
-        <v>0</v>
-      </c>
-      <c r="I31" s="34">
-        <v>0</v>
-      </c>
-      <c r="J31" s="30" t="s">
-        <v>77</v>
-      </c>
-      <c r="K31" s="34">
-        <v>0</v>
-      </c>
-      <c r="L31" s="35" t="s">
-        <v>77</v>
+      <c r="G31" s="31">
+        <v>0</v>
+      </c>
+      <c r="H31" s="19">
+        <v>0</v>
+      </c>
+      <c r="I31" s="32">
+        <v>0</v>
+      </c>
+      <c r="J31" s="28" t="s">
+        <v>81</v>
+      </c>
+      <c r="K31" s="32">
+        <v>0</v>
+      </c>
+      <c r="L31" s="33" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="B32" s="30">
+        <v>104</v>
+      </c>
+      <c r="B32" s="28">
         <v>46254.5</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="D32" s="31">
+        <v>105</v>
+      </c>
+      <c r="D32" s="29">
         <v>1</v>
       </c>
-      <c r="E32" s="21">
+      <c r="E32" s="19">
         <v>825</v>
       </c>
-      <c r="F32" s="32">
+      <c r="F32" s="30">
         <v>825</v>
       </c>
-      <c r="G32" s="33">
-        <v>0</v>
-      </c>
-      <c r="H32" s="21">
-        <v>0</v>
-      </c>
-      <c r="I32" s="34">
-        <v>0</v>
-      </c>
-      <c r="J32" s="30" t="s">
-        <v>77</v>
-      </c>
-      <c r="K32" s="34">
-        <v>0</v>
-      </c>
-      <c r="L32" s="35" t="s">
-        <v>78</v>
+      <c r="G32" s="31">
+        <v>0</v>
+      </c>
+      <c r="H32" s="19">
+        <v>0</v>
+      </c>
+      <c r="I32" s="32">
+        <v>0</v>
+      </c>
+      <c r="J32" s="28" t="s">
+        <v>81</v>
+      </c>
+      <c r="K32" s="32">
+        <v>0</v>
+      </c>
+      <c r="L32" s="33" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="B33" s="30">
+        <v>62</v>
+      </c>
+      <c r="B33" s="28">
         <v>46255.5</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="D33" s="31">
+        <v>61</v>
+      </c>
+      <c r="D33" s="29">
         <v>2</v>
       </c>
-      <c r="E33" s="21">
+      <c r="E33" s="19">
         <v>1650</v>
       </c>
-      <c r="F33" s="32">
+      <c r="F33" s="30">
         <v>450</v>
       </c>
-      <c r="G33" s="33">
+      <c r="G33" s="31">
         <v>1200</v>
       </c>
-      <c r="H33" s="21">
+      <c r="H33" s="19">
         <v>1200</v>
       </c>
-      <c r="I33" s="23">
+      <c r="I33" s="21">
         <v>1200</v>
       </c>
-      <c r="J33" s="30">
+      <c r="J33" s="28">
         <v>46262.5</v>
       </c>
-      <c r="K33" s="34">
-        <v>0</v>
-      </c>
-      <c r="L33" s="35" t="s">
-        <v>77</v>
+      <c r="K33" s="32">
+        <v>0</v>
+      </c>
+      <c r="L33" s="33" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="B34" s="30">
+        <v>106</v>
+      </c>
+      <c r="B34" s="28">
         <v>46255.5</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="D34" s="31">
+        <v>107</v>
+      </c>
+      <c r="D34" s="29">
         <v>4</v>
       </c>
-      <c r="E34" s="21">
+      <c r="E34" s="19">
         <v>3300</v>
       </c>
-      <c r="F34" s="32">
+      <c r="F34" s="30">
         <v>3300</v>
       </c>
-      <c r="G34" s="33">
-        <v>0</v>
-      </c>
-      <c r="H34" s="21">
-        <v>0</v>
-      </c>
-      <c r="I34" s="34">
-        <v>0</v>
-      </c>
-      <c r="J34" s="30" t="s">
-        <v>77</v>
-      </c>
-      <c r="K34" s="34">
-        <v>0</v>
-      </c>
-      <c r="L34" s="35" t="s">
-        <v>86</v>
+      <c r="G34" s="31">
+        <v>0</v>
+      </c>
+      <c r="H34" s="19">
+        <v>0</v>
+      </c>
+      <c r="I34" s="32">
+        <v>0</v>
+      </c>
+      <c r="J34" s="28" t="s">
+        <v>81</v>
+      </c>
+      <c r="K34" s="32">
+        <v>0</v>
+      </c>
+      <c r="L34" s="33" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="B35" s="30">
+        <v>108</v>
+      </c>
+      <c r="B35" s="28">
         <v>46255.5</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="D35" s="31">
+        <v>107</v>
+      </c>
+      <c r="D35" s="29">
         <v>16</v>
       </c>
-      <c r="E35" s="21">
+      <c r="E35" s="19">
         <v>13200</v>
       </c>
-      <c r="F35" s="32">
+      <c r="F35" s="30">
         <v>3600</v>
       </c>
-      <c r="G35" s="33">
+      <c r="G35" s="31">
         <v>9600</v>
       </c>
-      <c r="H35" s="21">
+      <c r="H35" s="19">
         <v>9600</v>
       </c>
-      <c r="I35" s="23">
+      <c r="I35" s="21">
         <v>9600</v>
       </c>
-      <c r="J35" s="30">
+      <c r="J35" s="28">
         <v>46268.5</v>
       </c>
-      <c r="K35" s="34">
-        <v>0</v>
-      </c>
-      <c r="L35" s="35" t="s">
-        <v>77</v>
+      <c r="K35" s="32">
+        <v>0</v>
+      </c>
+      <c r="L35" s="33" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="B36" s="30">
+        <v>109</v>
+      </c>
+      <c r="B36" s="28">
         <v>46258.5</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="D36" s="31">
+        <v>102</v>
+      </c>
+      <c r="D36" s="29">
         <v>2</v>
       </c>
-      <c r="E36" s="21">
+      <c r="E36" s="19">
         <v>1650</v>
       </c>
-      <c r="F36" s="32">
+      <c r="F36" s="30">
         <v>1650</v>
       </c>
-      <c r="G36" s="33">
-        <v>0</v>
-      </c>
-      <c r="H36" s="21">
-        <v>0</v>
-      </c>
-      <c r="I36" s="34">
-        <v>0</v>
-      </c>
-      <c r="J36" s="30" t="s">
-        <v>77</v>
-      </c>
-      <c r="K36" s="34">
-        <v>0</v>
-      </c>
-      <c r="L36" s="35" t="s">
-        <v>86</v>
+      <c r="G36" s="31">
+        <v>0</v>
+      </c>
+      <c r="H36" s="19">
+        <v>0</v>
+      </c>
+      <c r="I36" s="32">
+        <v>0</v>
+      </c>
+      <c r="J36" s="28" t="s">
+        <v>81</v>
+      </c>
+      <c r="K36" s="32">
+        <v>0</v>
+      </c>
+      <c r="L36" s="33" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="B37" s="30">
+        <v>110</v>
+      </c>
+      <c r="B37" s="28">
         <v>46258.5</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="D37" s="31">
+        <v>102</v>
+      </c>
+      <c r="D37" s="29">
         <v>8</v>
       </c>
-      <c r="E37" s="21">
+      <c r="E37" s="19">
         <v>6600</v>
       </c>
-      <c r="F37" s="32">
+      <c r="F37" s="30">
         <v>1800</v>
       </c>
-      <c r="G37" s="33">
+      <c r="G37" s="31">
         <v>4800</v>
       </c>
-      <c r="H37" s="21">
+      <c r="H37" s="19">
         <v>4800</v>
       </c>
-      <c r="I37" s="34">
-        <v>0</v>
-      </c>
-      <c r="J37" s="30" t="s">
-        <v>77</v>
-      </c>
-      <c r="K37" s="36">
+      <c r="I37" s="21">
         <v>4800</v>
       </c>
-      <c r="L37" s="35" t="s">
-        <v>77</v>
+      <c r="J37" s="28">
+        <v>46296.5</v>
+      </c>
+      <c r="K37" s="32">
+        <v>0</v>
+      </c>
+      <c r="L37" s="33" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="B38" s="30">
+        <v>111</v>
+      </c>
+      <c r="B38" s="28">
         <v>46259.5</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="D38" s="31">
+        <v>39</v>
+      </c>
+      <c r="D38" s="29">
         <v>5</v>
       </c>
-      <c r="E38" s="21">
+      <c r="E38" s="19">
         <v>4125</v>
       </c>
-      <c r="F38" s="32">
+      <c r="F38" s="30">
         <v>1125</v>
       </c>
-      <c r="G38" s="33">
+      <c r="G38" s="31">
         <v>3000</v>
       </c>
-      <c r="H38" s="21">
+      <c r="H38" s="19">
         <v>3000</v>
       </c>
-      <c r="I38" s="34">
-        <v>0</v>
-      </c>
-      <c r="J38" s="30" t="s">
-        <v>77</v>
-      </c>
-      <c r="K38" s="36">
+      <c r="I38" s="32">
+        <v>0</v>
+      </c>
+      <c r="J38" s="28" t="s">
+        <v>81</v>
+      </c>
+      <c r="K38" s="34">
         <v>3000</v>
       </c>
-      <c r="L38" s="35" t="s">
-        <v>77</v>
+      <c r="L38" s="33" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="B39" s="30">
+        <v>112</v>
+      </c>
+      <c r="B39" s="28">
         <v>46259.5</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="D39" s="31">
+        <v>113</v>
+      </c>
+      <c r="D39" s="29">
         <v>1</v>
       </c>
-      <c r="E39" s="21">
+      <c r="E39" s="19">
         <v>825</v>
       </c>
-      <c r="F39" s="32">
+      <c r="F39" s="30">
         <v>825</v>
       </c>
-      <c r="G39" s="33">
-        <v>0</v>
-      </c>
-      <c r="H39" s="21">
-        <v>0</v>
-      </c>
-      <c r="I39" s="34">
-        <v>0</v>
-      </c>
-      <c r="J39" s="30" t="s">
-        <v>77</v>
-      </c>
-      <c r="K39" s="34">
-        <v>0</v>
-      </c>
-      <c r="L39" s="35" t="s">
-        <v>78</v>
+      <c r="G39" s="31">
+        <v>0</v>
+      </c>
+      <c r="H39" s="19">
+        <v>0</v>
+      </c>
+      <c r="I39" s="32">
+        <v>0</v>
+      </c>
+      <c r="J39" s="28" t="s">
+        <v>81</v>
+      </c>
+      <c r="K39" s="32">
+        <v>0</v>
+      </c>
+      <c r="L39" s="33" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A40" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="B40" s="30">
+        <v>114</v>
+      </c>
+      <c r="B40" s="28">
         <v>46259.5</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="D40" s="31">
+        <v>115</v>
+      </c>
+      <c r="D40" s="29">
         <v>1</v>
       </c>
-      <c r="E40" s="21">
+      <c r="E40" s="19">
         <v>825</v>
       </c>
-      <c r="F40" s="32">
+      <c r="F40" s="30">
         <v>150</v>
       </c>
-      <c r="G40" s="33">
+      <c r="G40" s="31">
         <v>675</v>
       </c>
-      <c r="H40" s="21">
+      <c r="H40" s="19">
         <v>600</v>
       </c>
-      <c r="I40" s="23">
+      <c r="I40" s="21">
         <v>675</v>
       </c>
-      <c r="J40" s="30">
+      <c r="J40" s="28">
         <v>46266.5</v>
       </c>
-      <c r="K40" s="34">
-        <v>0</v>
-      </c>
-      <c r="L40" s="35" t="s">
-        <v>77</v>
+      <c r="K40" s="32">
+        <v>0</v>
+      </c>
+      <c r="L40" s="33" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A41" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="B41" s="30">
+        <v>116</v>
+      </c>
+      <c r="B41" s="28">
         <v>46261.5</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="D41" s="31">
+        <v>117</v>
+      </c>
+      <c r="D41" s="29">
         <v>2</v>
       </c>
-      <c r="E41" s="21">
+      <c r="E41" s="19">
         <v>1650</v>
       </c>
-      <c r="F41" s="32">
+      <c r="F41" s="30">
         <v>450</v>
       </c>
-      <c r="G41" s="33">
+      <c r="G41" s="31">
         <v>1200</v>
       </c>
-      <c r="H41" s="21">
+      <c r="H41" s="19">
         <v>1200</v>
       </c>
-      <c r="I41" s="34">
-        <v>0</v>
-      </c>
-      <c r="J41" s="30" t="s">
-        <v>77</v>
-      </c>
-      <c r="K41" s="36">
+      <c r="I41" s="32">
+        <v>0</v>
+      </c>
+      <c r="J41" s="28" t="s">
+        <v>81</v>
+      </c>
+      <c r="K41" s="34">
         <v>1200</v>
       </c>
-      <c r="L41" s="35" t="s">
-        <v>77</v>
+      <c r="L41" s="33" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="B42" s="30">
+        <v>118</v>
+      </c>
+      <c r="B42" s="28">
         <v>46261.5</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="D42" s="31">
+        <v>119</v>
+      </c>
+      <c r="D42" s="29">
         <v>1</v>
       </c>
-      <c r="E42" s="21">
+      <c r="E42" s="19">
         <v>825</v>
       </c>
-      <c r="F42" s="32">
+      <c r="F42" s="30">
         <v>225</v>
       </c>
-      <c r="G42" s="33">
+      <c r="G42" s="31">
         <v>600</v>
       </c>
-      <c r="H42" s="21">
+      <c r="H42" s="19">
         <v>600</v>
       </c>
-      <c r="I42" s="34">
-        <v>0</v>
-      </c>
-      <c r="J42" s="30" t="s">
-        <v>77</v>
-      </c>
-      <c r="K42" s="36">
+      <c r="I42" s="32">
+        <v>0</v>
+      </c>
+      <c r="J42" s="28" t="s">
+        <v>81</v>
+      </c>
+      <c r="K42" s="34">
         <v>600</v>
       </c>
-      <c r="L42" s="35" t="s">
-        <v>77</v>
+      <c r="L42" s="33" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="B43" s="30">
+        <v>120</v>
+      </c>
+      <c r="B43" s="28">
         <v>46261.5</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="D43" s="31">
+        <v>119</v>
+      </c>
+      <c r="D43" s="29">
         <v>3</v>
       </c>
-      <c r="E43" s="21">
+      <c r="E43" s="19">
         <v>2475</v>
       </c>
-      <c r="F43" s="32">
+      <c r="F43" s="30">
         <v>2475</v>
       </c>
-      <c r="G43" s="33">
-        <v>0</v>
-      </c>
-      <c r="H43" s="21">
-        <v>0</v>
-      </c>
-      <c r="I43" s="34">
-        <v>0</v>
-      </c>
-      <c r="J43" s="30" t="s">
-        <v>77</v>
-      </c>
-      <c r="K43" s="34">
-        <v>0</v>
-      </c>
-      <c r="L43" s="35" t="s">
-        <v>78</v>
+      <c r="G43" s="31">
+        <v>0</v>
+      </c>
+      <c r="H43" s="19">
+        <v>0</v>
+      </c>
+      <c r="I43" s="32">
+        <v>0</v>
+      </c>
+      <c r="J43" s="28" t="s">
+        <v>81</v>
+      </c>
+      <c r="K43" s="32">
+        <v>0</v>
+      </c>
+      <c r="L43" s="33" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="B44" s="30">
+        <v>121</v>
+      </c>
+      <c r="B44" s="28">
         <v>46261.5</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="D44" s="31">
+        <v>119</v>
+      </c>
+      <c r="D44" s="29">
         <v>7</v>
       </c>
-      <c r="E44" s="21">
+      <c r="E44" s="19">
         <v>5775</v>
       </c>
-      <c r="F44" s="32">
+      <c r="F44" s="30">
         <v>1575</v>
       </c>
-      <c r="G44" s="33">
+      <c r="G44" s="31">
         <v>4200</v>
       </c>
-      <c r="H44" s="21">
+      <c r="H44" s="19">
         <v>4200</v>
       </c>
-      <c r="I44" s="23">
+      <c r="I44" s="21">
         <v>4200</v>
       </c>
-      <c r="J44" s="30">
+      <c r="J44" s="28">
         <v>46280.5</v>
       </c>
-      <c r="K44" s="34">
-        <v>0</v>
-      </c>
-      <c r="L44" s="35" t="s">
-        <v>77</v>
+      <c r="K44" s="32">
+        <v>0</v>
+      </c>
+      <c r="L44" s="33" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A45" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="B45" s="30">
+        <v>122</v>
+      </c>
+      <c r="B45" s="28">
         <v>46265.5</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="D45" s="31">
+        <v>123</v>
+      </c>
+      <c r="D45" s="29">
         <v>1</v>
       </c>
-      <c r="E45" s="21">
+      <c r="E45" s="19">
         <v>825</v>
       </c>
-      <c r="F45" s="32">
+      <c r="F45" s="30">
         <v>825</v>
       </c>
-      <c r="G45" s="33">
-        <v>0</v>
-      </c>
-      <c r="H45" s="21">
-        <v>0</v>
-      </c>
-      <c r="I45" s="34">
-        <v>0</v>
-      </c>
-      <c r="J45" s="30" t="s">
-        <v>77</v>
-      </c>
-      <c r="K45" s="34">
-        <v>0</v>
-      </c>
-      <c r="L45" s="35" t="s">
-        <v>86</v>
+      <c r="G45" s="31">
+        <v>0</v>
+      </c>
+      <c r="H45" s="19">
+        <v>0</v>
+      </c>
+      <c r="I45" s="32">
+        <v>0</v>
+      </c>
+      <c r="J45" s="28" t="s">
+        <v>81</v>
+      </c>
+      <c r="K45" s="32">
+        <v>0</v>
+      </c>
+      <c r="L45" s="33" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A47" s="37" t="s">
-        <v>61</v>
-      </c>
-      <c r="C47" s="11" t="s">
-        <v>120</v>
-      </c>
-      <c r="D47" s="38">
+      <c r="A47" s="35" t="s">
+        <v>65</v>
+      </c>
+      <c r="C47" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="D47" s="36">
         <v>172</v>
       </c>
-      <c r="E47" s="33">
+      <c r="E47" s="31">
         <v>141900</v>
       </c>
-      <c r="F47" s="39">
+      <c r="F47" s="37">
         <v>63525</v>
       </c>
-      <c r="G47" s="40">
+      <c r="G47" s="38">
         <v>78375</v>
       </c>
-      <c r="H47" s="33">
+      <c r="H47" s="31">
         <v>78300</v>
       </c>
-      <c r="I47" s="41">
-        <v>62936.46000000001</v>
-      </c>
-      <c r="K47" s="42">
-        <v>15600</v>
+      <c r="I47" s="39">
+        <v>73736.46</v>
+      </c>
+      <c r="K47" s="40">
+        <v>4800</v>
       </c>
     </row>
   </sheetData>
